--- a/outputs/01a0c95f-3b4f-7762-ad52-61bb13941fcc/装修需求采集表_字段清单_V2.xlsx
+++ b/outputs/01a0c95f-3b4f-7762-ad52-61bb13941fcc/装修需求采集表_字段清单_V2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表单字段" sheetId="1" r:id="Ra2b43bfcbb97435f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量房确认清单" sheetId="2" r:id="R18218e33921c4ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表单字段" sheetId="1" r:id="Rd06b665b98c644d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量房确认清单" sheetId="2" r:id="Rbbbc7928b446420f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -595,7 +595,7 @@
         <x:v>㎡</x:v>
       </x:c>
       <x:c r="G7" s="25" t="str">
-        <x:v>选填</x:v>
+        <x:v>推荐填写</x:v>
       </x:c>
       <x:c r="H7" s="25" t="str">
         <x:v>固定</x:v>
@@ -705,7 +705,7 @@
         <x:v>毛坯 / 旧房翻新 / 精装改造 / 不清楚</x:v>
       </x:c>
       <x:c r="G10" s="25" t="str">
-        <x:v>选填</x:v>
+        <x:v>推荐填写</x:v>
       </x:c>
       <x:c r="H10" s="25" t="str">
         <x:v>固定</x:v>
@@ -957,7 +957,7 @@
         <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G17" s="25" t="str">
-        <x:v>选填</x:v>
+        <x:v>推荐填写</x:v>
       </x:c>
       <x:c r="H17" s="25" t="str">
         <x:v>固定</x:v>
@@ -1393,7 +1393,7 @@
         <x:v>年-月</x:v>
       </x:c>
       <x:c r="G29" s="25" t="str">
-        <x:v>选填</x:v>
+        <x:v>推荐填写</x:v>
       </x:c>
       <x:c r="H29" s="25" t="str">
         <x:v>固定</x:v>
@@ -1789,7 +1789,7 @@
         <x:v>超预算 / 工期延误 / 增项 / 施工质量 / 环保污染 / 效果不符 / 说不上来</x:v>
       </x:c>
       <x:c r="G40" s="25" t="str">
-        <x:v>推荐填写</x:v>
+        <x:v>选填</x:v>
       </x:c>
       <x:c r="H40" s="25" t="str">
         <x:v>固定</x:v>
@@ -2021,96 +2021,98 @@
       </x:c>
       <x:c r="L46" s="22" t="str"/>
     </x:row>
-    <x:row r="47" ht="84" hidden="0" customHeight="1">
-      <x:c r="A47" s="27" t="str">
+    <x:row r="47" ht="36" hidden="0" customHeight="1">
+      <x:c r="A47" s="19" t="str">
+        <x:v>base_other</x:v>
+      </x:c>
+      <x:c r="B47" s="19" t="str">
+        <x:v>认识你家</x:v>
+      </x:c>
+      <x:c r="C47" s="19" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="D47" s="19" t="str">
+        <x:v>其他补充</x:v>
+      </x:c>
+      <x:c r="E47" s="19" t="str">
+        <x:v>长文本</x:v>
+      </x:c>
+      <x:c r="F47" s="22" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="G47" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H47" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I47" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J47" s="22" t="str">
+        <x:v>个性化需求或特殊说明</x:v>
+      </x:c>
+      <x:c r="K47" s="19" t="str">
+        <x:v>本次重构</x:v>
+      </x:c>
+      <x:c r="L47" s="22" t="str">
+        <x:v>助手建议会写回这里</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="84" hidden="0" customHeight="1">
+      <x:c r="A48" s="27" t="str">
         <x:v>dev_ac</x:v>
       </x:c>
-      <x:c r="B47" s="27" t="str">
+      <x:c r="B48" s="27" t="str">
         <x:v>设备与系统</x:v>
       </x:c>
-      <x:c r="C47" s="27" t="str">
+      <x:c r="C48" s="27" t="str">
         <x:v>空调与采暖</x:v>
       </x:c>
-      <x:c r="D47" s="27" t="str">
+      <x:c r="D48" s="27" t="str">
         <x:v>空调需求</x:v>
       </x:c>
-      <x:c r="E47" s="27" t="str">
+      <x:c r="E48" s="27" t="str">
         <x:v>多选</x:v>
       </x:c>
-      <x:c r="F47" s="28" t="str">
+      <x:c r="F48" s="28" t="str">
         <x:v>中央空调 / 普通空调（挂机柜机） / 不确定，听设计师建议</x:v>
       </x:c>
-      <x:c r="G47" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H47" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I47" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J47" s="28" t="str">
+      <x:c r="G48" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H48" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I48" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J48" s="28" t="str">
         <x:v>吊顶、回风口、检修口预留</x:v>
       </x:c>
-      <x:c r="K47" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L47" s="28" t="str"/>
-    </x:row>
-    <x:row r="48" ht="48" hidden="0" customHeight="1">
-      <x:c r="A48" s="19" t="str">
+      <x:c r="K48" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L48" s="28" t="str"/>
+    </x:row>
+    <x:row r="49" ht="48" hidden="0" customHeight="1">
+      <x:c r="A49" s="19" t="str">
         <x:v>dev_freshair</x:v>
-      </x:c>
-      <x:c r="B48" s="19" t="str">
-        <x:v>设备与系统</x:v>
-      </x:c>
-      <x:c r="C48" s="19" t="str">
-        <x:v>空调与采暖</x:v>
-      </x:c>
-      <x:c r="D48" s="19" t="str">
-        <x:v>新风系统</x:v>
-      </x:c>
-      <x:c r="E48" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F48" s="22" t="str">
-        <x:v>需要 / 不需要 / 不确定</x:v>
-      </x:c>
-      <x:c r="G48" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H48" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I48" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J48" s="22" t="str">
-        <x:v>吊顶走管、墙面开孔、滤网检修口</x:v>
-      </x:c>
-      <x:c r="K48" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L48" s="22" t="str"/>
-    </x:row>
-    <x:row r="49" ht="96" hidden="0" customHeight="1">
-      <x:c r="A49" s="19" t="str">
-        <x:v>dev_water</x:v>
       </x:c>
       <x:c r="B49" s="19" t="str">
         <x:v>设备与系统</x:v>
       </x:c>
       <x:c r="C49" s="19" t="str">
-        <x:v>水与热水</x:v>
+        <x:v>空调与采暖</x:v>
       </x:c>
       <x:c r="D49" s="19" t="str">
-        <x:v>水质与饮水需求</x:v>
+        <x:v>新风系统</x:v>
       </x:c>
       <x:c r="E49" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F49" s="22" t="str">
-        <x:v>想喝直饮水（净水） / 水垢重，想做软水 / 不清楚，听设计师建议</x:v>
+        <x:v>需要 / 不需要 / 不确定</x:v>
       </x:c>
       <x:c r="G49" s="25" t="str">
         <x:v>选填</x:v>
@@ -2122,18 +2124,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J49" s="22" t="str">
-        <x:v>水电点位、橱柜下空间</x:v>
+        <x:v>吊顶走管、墙面开孔、滤网检修口</x:v>
       </x:c>
       <x:c r="K49" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
-      <x:c r="L49" s="22" t="str">
-        <x:v>与厨房净水需求合并，避免重复填报</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="48" hidden="0" customHeight="1">
+      <x:c r="L49" s="22" t="str"/>
+    </x:row>
+    <x:row r="50" ht="96" hidden="0" customHeight="1">
       <x:c r="A50" s="19" t="str">
-        <x:v>dev_hotwater</x:v>
+        <x:v>dev_water</x:v>
       </x:c>
       <x:c r="B50" s="19" t="str">
         <x:v>设备与系统</x:v>
@@ -2142,13 +2142,13 @@
         <x:v>水与热水</x:v>
       </x:c>
       <x:c r="D50" s="19" t="str">
-        <x:v>生活热水偏好</x:v>
+        <x:v>水质与饮水需求</x:v>
       </x:c>
       <x:c r="E50" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F50" s="22" t="str">
-        <x:v>希望打开就有热水 / 无所谓 / 不确定</x:v>
+        <x:v>想喝直饮水（净水） / 水垢重，想做软水 / 不清楚，听设计师建议</x:v>
       </x:c>
       <x:c r="G50" s="25" t="str">
         <x:v>选填</x:v>
@@ -2160,16 +2160,18 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J50" s="22" t="str">
-        <x:v>回水管预留</x:v>
+        <x:v>水电点位、橱柜下空间</x:v>
       </x:c>
       <x:c r="K50" s="19" t="str">
-        <x:v>S3</x:v>
-      </x:c>
-      <x:c r="L50" s="22" t="str"/>
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L50" s="22" t="str">
+        <x:v>与厨房净水需求合并，避免重复填报</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="48" hidden="0" customHeight="1">
       <x:c r="A51" s="19" t="str">
-        <x:v>dev_drain</x:v>
+        <x:v>dev_hotwater</x:v>
       </x:c>
       <x:c r="B51" s="19" t="str">
         <x:v>设备与系统</x:v>
@@ -2178,13 +2180,13 @@
         <x:v>水与热水</x:v>
       </x:c>
       <x:c r="D51" s="19" t="str">
-        <x:v>排水特殊需求</x:v>
+        <x:v>生活热水偏好</x:v>
       </x:c>
       <x:c r="E51" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F51" s="22" t="str">
-        <x:v>干区地漏 / 墙排水 / 露天阳台排水</x:v>
+        <x:v>希望打开就有热水 / 无所谓 / 不确定</x:v>
       </x:c>
       <x:c r="G51" s="25" t="str">
         <x:v>选填</x:v>
@@ -2196,31 +2198,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J51" s="22" t="str">
-        <x:v>排水点位预留</x:v>
+        <x:v>回水管预留</x:v>
       </x:c>
       <x:c r="K51" s="19" t="str">
         <x:v>S3</x:v>
       </x:c>
       <x:c r="L51" s="22" t="str"/>
     </x:row>
-    <x:row r="52" ht="72" hidden="0" customHeight="1">
+    <x:row r="52" ht="48" hidden="0" customHeight="1">
       <x:c r="A52" s="19" t="str">
-        <x:v>dev_smart</x:v>
+        <x:v>dev_drain</x:v>
       </x:c>
       <x:c r="B52" s="19" t="str">
         <x:v>设备与系统</x:v>
       </x:c>
       <x:c r="C52" s="19" t="str">
-        <x:v>智能与弱电</x:v>
+        <x:v>水与热水</x:v>
       </x:c>
       <x:c r="D52" s="19" t="str">
-        <x:v>智能与网络需求</x:v>
+        <x:v>排水特殊需求</x:v>
       </x:c>
       <x:c r="E52" s="19" t="str">
         <x:v>多选</x:v>
       </x:c>
       <x:c r="F52" s="22" t="str">
-        <x:v>智能灯光 / 电动窗帘 / 全屋WIFI / 全屋监控 / 智能门锁 / 背景音响</x:v>
+        <x:v>干区地漏 / 墙排水 / 露天阳台排水</x:v>
       </x:c>
       <x:c r="G52" s="25" t="str">
         <x:v>选填</x:v>
@@ -2232,16 +2234,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J52" s="22" t="str">
-        <x:v>预留电源与点位</x:v>
+        <x:v>排水点位预留</x:v>
       </x:c>
       <x:c r="K52" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L52" s="22" t="str"/>
     </x:row>
-    <x:row r="53" ht="48" hidden="0" customHeight="1">
+    <x:row r="53" ht="72" hidden="0" customHeight="1">
       <x:c r="A53" s="19" t="str">
-        <x:v>dev_circuit</x:v>
+        <x:v>dev_smart</x:v>
       </x:c>
       <x:c r="B53" s="19" t="str">
         <x:v>设备与系统</x:v>
@@ -2250,13 +2252,13 @@
         <x:v>智能与弱电</x:v>
       </x:c>
       <x:c r="D53" s="19" t="str">
-        <x:v>生活便利类电路需求</x:v>
+        <x:v>智能与网络需求</x:v>
       </x:c>
       <x:c r="E53" s="19" t="str">
         <x:v>多选</x:v>
       </x:c>
       <x:c r="F53" s="22" t="str">
-        <x:v>起夜灯 / 感应灯 / USB插座 / 背景音乐</x:v>
+        <x:v>智能灯光 / 电动窗帘 / 全屋WIFI / 全屋监控 / 智能门锁 / 背景音响</x:v>
       </x:c>
       <x:c r="G53" s="25" t="str">
         <x:v>选填</x:v>
@@ -2268,16 +2270,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J53" s="22" t="str">
-        <x:v>插座与灯位点位</x:v>
+        <x:v>预留电源与点位</x:v>
       </x:c>
       <x:c r="K53" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L53" s="22" t="str"/>
     </x:row>
-    <x:row r="54" ht="15" hidden="0" customHeight="1">
+    <x:row r="54" ht="48" hidden="0" customHeight="1">
       <x:c r="A54" s="19" t="str">
-        <x:v>dev_other</x:v>
+        <x:v>dev_circuit</x:v>
       </x:c>
       <x:c r="B54" s="19" t="str">
         <x:v>设备与系统</x:v>
@@ -2286,13 +2288,13 @@
         <x:v>智能与弱电</x:v>
       </x:c>
       <x:c r="D54" s="19" t="str">
-        <x:v>其他补充</x:v>
+        <x:v>生活便利类电路需求</x:v>
       </x:c>
       <x:c r="E54" s="19" t="str">
-        <x:v>长文本</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F54" s="22" t="str">
-        <x:v>文本</x:v>
+        <x:v>起夜灯 / 感应灯 / USB插座 / 背景音乐</x:v>
       </x:c>
       <x:c r="G54" s="25" t="str">
         <x:v>选填</x:v>
@@ -2304,141 +2306,141 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J54" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>插座与灯位点位</x:v>
       </x:c>
       <x:c r="K54" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L54" s="22" t="str"/>
     </x:row>
-    <x:row r="55" ht="60" hidden="0" customHeight="1">
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="19" t="str">
-        <x:v>dev_heat</x:v>
+        <x:v>dev_other</x:v>
       </x:c>
       <x:c r="B55" s="19" t="str">
         <x:v>设备与系统</x:v>
       </x:c>
       <x:c r="C55" s="19" t="str">
+        <x:v>智能与弱电</x:v>
+      </x:c>
+      <x:c r="D55" s="19" t="str">
+        <x:v>其他补充</x:v>
+      </x:c>
+      <x:c r="E55" s="19" t="str">
+        <x:v>长文本</x:v>
+      </x:c>
+      <x:c r="F55" s="22" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="G55" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H55" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I55" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J55" s="22" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K55" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L55" s="22" t="str"/>
+    </x:row>
+    <x:row r="56" ht="60" hidden="0" customHeight="1">
+      <x:c r="A56" s="19" t="str">
+        <x:v>dev_heat</x:v>
+      </x:c>
+      <x:c r="B56" s="19" t="str">
+        <x:v>设备与系统</x:v>
+      </x:c>
+      <x:c r="C56" s="19" t="str">
         <x:v>空调与采暖</x:v>
       </x:c>
-      <x:c r="D55" s="19" t="str">
+      <x:c r="D56" s="19" t="str">
         <x:v>取暖方式</x:v>
       </x:c>
-      <x:c r="E55" s="19" t="str">
+      <x:c r="E56" s="19" t="str">
         <x:v>多选</x:v>
       </x:c>
-      <x:c r="F55" s="22" t="str">
+      <x:c r="F56" s="22" t="str">
         <x:v>地暖 / 暖气片墙暖 / 只靠空调 / 不确定</x:v>
       </x:c>
-      <x:c r="G55" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H55" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I55" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J55" s="22" t="str">
+      <x:c r="G56" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H56" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I56" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J56" s="22" t="str">
         <x:v>地面抬高与地板材质</x:v>
       </x:c>
-      <x:c r="K55" s="19" t="str">
+      <x:c r="K56" s="19" t="str">
         <x:v>本次重构</x:v>
       </x:c>
-      <x:c r="L55" s="22" t="str">
+      <x:c r="L56" s="22" t="str">
         <x:v>原「地暖」「墙暖」两项合并</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="24" hidden="0" customHeight="1">
-      <x:c r="A56" s="27" t="str">
+    <x:row r="57" ht="24" hidden="0" customHeight="1">
+      <x:c r="A57" s="27" t="str">
         <x:v>ex_main</x:v>
       </x:c>
-      <x:c r="B56" s="27" t="str">
+      <x:c r="B57" s="27" t="str">
         <x:v>玄关</x:v>
       </x:c>
-      <x:c r="C56" s="27" t="str">
+      <x:c r="C57" s="27" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="D56" s="27" t="str">
+      <x:c r="D57" s="27" t="str">
         <x:v>玄关定位</x:v>
       </x:c>
-      <x:c r="E56" s="27" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F56" s="28" t="str">
+      <x:c r="E57" s="27" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F57" s="28" t="str">
         <x:v>实用为主 / 装饰为主</x:v>
       </x:c>
-      <x:c r="G56" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H56" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I56" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J56" s="28" t="str">
+      <x:c r="G57" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H57" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I57" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J57" s="28" t="str">
         <x:v>收纳量与造型投入</x:v>
       </x:c>
-      <x:c r="K56" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L56" s="28" t="str"/>
-    </x:row>
-    <x:row r="57" ht="48" hidden="0" customHeight="1">
-      <x:c r="A57" s="19" t="str">
+      <x:c r="K57" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L57" s="28" t="str"/>
+    </x:row>
+    <x:row r="58" ht="48" hidden="0" customHeight="1">
+      <x:c r="A58" s="19" t="str">
         <x:v>ex_first</x:v>
-      </x:c>
-      <x:c r="B57" s="19" t="str">
-        <x:v>玄关</x:v>
-      </x:c>
-      <x:c r="C57" s="19" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D57" s="19" t="str">
-        <x:v>回家第一件事</x:v>
-      </x:c>
-      <x:c r="E57" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F57" s="22" t="str">
-        <x:v>立即换家居服 / 放下包再说</x:v>
-      </x:c>
-      <x:c r="G57" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H57" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I57" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J57" s="22" t="str">
-        <x:v>玄关挂衣与收纳分区</x:v>
-      </x:c>
-      <x:c r="K57" s="19" t="str">
-        <x:v>S5</x:v>
-      </x:c>
-      <x:c r="L57" s="22" t="str"/>
-    </x:row>
-    <x:row r="58" ht="24" hidden="0" customHeight="1">
-      <x:c r="A58" s="19" t="str">
-        <x:v>ex_coat</x:v>
       </x:c>
       <x:c r="B58" s="19" t="str">
         <x:v>玄关</x:v>
       </x:c>
       <x:c r="C58" s="19" t="str">
-        <x:v>收纳</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="D58" s="19" t="str">
-        <x:v>外套与包包区</x:v>
+        <x:v>回家第一件事</x:v>
       </x:c>
       <x:c r="E58" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F58" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>立即换家居服 / 放下包再说</x:v>
       </x:c>
       <x:c r="G58" s="25" t="str">
         <x:v>选填</x:v>
@@ -2450,16 +2452,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J58" s="22" t="str">
-        <x:v>挂衣区与挂钩</x:v>
+        <x:v>玄关挂衣与收纳分区</x:v>
       </x:c>
       <x:c r="K58" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L58" s="22" t="str"/>
     </x:row>
-    <x:row r="59" ht="36" hidden="0" customHeight="1">
+    <x:row r="59" ht="24" hidden="0" customHeight="1">
       <x:c r="A59" s="19" t="str">
-        <x:v>ex_mirror</x:v>
+        <x:v>ex_coat</x:v>
       </x:c>
       <x:c r="B59" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2468,7 +2470,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D59" s="19" t="str">
-        <x:v>全身镜</x:v>
+        <x:v>外套与包包区</x:v>
       </x:c>
       <x:c r="E59" s="19" t="str">
         <x:v>单选</x:v>
@@ -2486,7 +2488,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J59" s="22" t="str">
-        <x:v>镜面位置与风水避让</x:v>
+        <x:v>挂衣区与挂钩</x:v>
       </x:c>
       <x:c r="K59" s="19" t="str">
         <x:v>原件</x:v>
@@ -2495,7 +2497,7 @@
     </x:row>
     <x:row r="60" ht="36" hidden="0" customHeight="1">
       <x:c r="A60" s="19" t="str">
-        <x:v>ex_shoe</x:v>
+        <x:v>ex_mirror</x:v>
       </x:c>
       <x:c r="B60" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2504,7 +2506,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D60" s="19" t="str">
-        <x:v>鞋柜</x:v>
+        <x:v>全身镜</x:v>
       </x:c>
       <x:c r="E60" s="19" t="str">
         <x:v>单选</x:v>
@@ -2522,16 +2524,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J60" s="22" t="str">
-        <x:v>柜体容量与层板形式</x:v>
+        <x:v>镜面位置与风水避让</x:v>
       </x:c>
       <x:c r="K60" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L60" s="22" t="str"/>
     </x:row>
-    <x:row r="61" ht="24" hidden="0" customHeight="1">
+    <x:row r="61" ht="36" hidden="0" customHeight="1">
       <x:c r="A61" s="19" t="str">
-        <x:v>ex_shoe_count</x:v>
+        <x:v>ex_shoe</x:v>
       </x:c>
       <x:c r="B61" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2540,13 +2542,13 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D61" s="19" t="str">
-        <x:v>鞋子数量</x:v>
+        <x:v>鞋柜</x:v>
       </x:c>
       <x:c r="E61" s="19" t="str">
-        <x:v>数字</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F61" s="22" t="str">
-        <x:v>双</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G61" s="25" t="str">
         <x:v>选填</x:v>
@@ -2558,16 +2560,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J61" s="22" t="str">
-        <x:v>柜体容量计算</x:v>
+        <x:v>柜体容量与层板形式</x:v>
       </x:c>
       <x:c r="K61" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L61" s="22" t="str"/>
     </x:row>
-    <x:row r="62" ht="36" hidden="0" customHeight="1">
+    <x:row r="62" ht="24" hidden="0" customHeight="1">
       <x:c r="A62" s="19" t="str">
-        <x:v>ex_boots</x:v>
+        <x:v>ex_shoe_count</x:v>
       </x:c>
       <x:c r="B62" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2576,7 +2578,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D62" s="19" t="str">
-        <x:v>高筒靴数量</x:v>
+        <x:v>鞋子数量</x:v>
       </x:c>
       <x:c r="E62" s="19" t="str">
         <x:v>数字</x:v>
@@ -2594,7 +2596,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J62" s="22" t="str">
-        <x:v>活动层板（&gt;30cm 层高）</x:v>
+        <x:v>柜体容量计算</x:v>
       </x:c>
       <x:c r="K62" s="19" t="str">
         <x:v>S4</x:v>
@@ -2603,7 +2605,7 @@
     </x:row>
     <x:row r="63" ht="36" hidden="0" customHeight="1">
       <x:c r="A63" s="19" t="str">
-        <x:v>ex_bench</x:v>
+        <x:v>ex_boots</x:v>
       </x:c>
       <x:c r="B63" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2612,13 +2614,13 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D63" s="19" t="str">
-        <x:v>换鞋凳</x:v>
+        <x:v>高筒靴数量</x:v>
       </x:c>
       <x:c r="E63" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>数字</x:v>
       </x:c>
       <x:c r="F63" s="22" t="str">
-        <x:v>固定 / 活动 / 不需要</x:v>
+        <x:v>双</x:v>
       </x:c>
       <x:c r="G63" s="25" t="str">
         <x:v>选填</x:v>
@@ -2630,16 +2632,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J63" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>活动层板（&gt;30cm 层高）</x:v>
       </x:c>
       <x:c r="K63" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S4</x:v>
       </x:c>
       <x:c r="L63" s="22" t="str"/>
     </x:row>
-    <x:row r="64" ht="24" hidden="0" customHeight="1">
+    <x:row r="64" ht="36" hidden="0" customHeight="1">
       <x:c r="A64" s="19" t="str">
-        <x:v>ex_storage</x:v>
+        <x:v>ex_bench</x:v>
       </x:c>
       <x:c r="B64" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2648,13 +2650,13 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D64" s="19" t="str">
-        <x:v>雨具与行李箱置物</x:v>
+        <x:v>换鞋凳</x:v>
       </x:c>
       <x:c r="E64" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F64" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>固定 / 活动 / 不需要</x:v>
       </x:c>
       <x:c r="G64" s="25" t="str">
         <x:v>选填</x:v>
@@ -2666,16 +2668,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J64" s="22" t="str">
-        <x:v>行李箱专属位置</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K64" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L64" s="22" t="str"/>
     </x:row>
     <x:row r="65" ht="24" hidden="0" customHeight="1">
       <x:c r="A65" s="19" t="str">
-        <x:v>ex_dryer</x:v>
+        <x:v>ex_storage</x:v>
       </x:c>
       <x:c r="B65" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2684,7 +2686,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D65" s="19" t="str">
-        <x:v>烘鞋器或充电插座</x:v>
+        <x:v>雨具与行李箱置物</x:v>
       </x:c>
       <x:c r="E65" s="19" t="str">
         <x:v>单选</x:v>
@@ -2702,16 +2704,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J65" s="22" t="str">
-        <x:v>玄关插座预留</x:v>
+        <x:v>行李箱专属位置</x:v>
       </x:c>
       <x:c r="K65" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>S4</x:v>
       </x:c>
       <x:c r="L65" s="22" t="str"/>
     </x:row>
     <x:row r="66" ht="24" hidden="0" customHeight="1">
       <x:c r="A66" s="19" t="str">
-        <x:v>ex_wardrobe</x:v>
+        <x:v>ex_dryer</x:v>
       </x:c>
       <x:c r="B66" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2720,7 +2722,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D66" s="19" t="str">
-        <x:v>入户衣柜</x:v>
+        <x:v>烘鞋器或充电插座</x:v>
       </x:c>
       <x:c r="E66" s="19" t="str">
         <x:v>单选</x:v>
@@ -2738,16 +2740,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J66" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>玄关插座预留</x:v>
       </x:c>
       <x:c r="K66" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L66" s="22" t="str"/>
     </x:row>
-    <x:row r="67" ht="36" hidden="0" customHeight="1">
+    <x:row r="67" ht="24" hidden="0" customHeight="1">
       <x:c r="A67" s="19" t="str">
-        <x:v>ex_desk</x:v>
+        <x:v>ex_wardrobe</x:v>
       </x:c>
       <x:c r="B67" s="19" t="str">
         <x:v>玄关</x:v>
@@ -2756,7 +2758,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D67" s="19" t="str">
-        <x:v>随手置物台面</x:v>
+        <x:v>入户衣柜</x:v>
       </x:c>
       <x:c r="E67" s="19" t="str">
         <x:v>单选</x:v>
@@ -2774,139 +2776,139 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J67" s="22" t="str">
-        <x:v>钥匙、快递临时放置</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K67" s="19" t="str">
         <x:v>S5</x:v>
       </x:c>
       <x:c r="L67" s="22" t="str"/>
     </x:row>
-    <x:row r="68" ht="15" hidden="0" customHeight="1">
+    <x:row r="68" ht="36" hidden="0" customHeight="1">
       <x:c r="A68" s="19" t="str">
-        <x:v>ex_other</x:v>
+        <x:v>ex_desk</x:v>
       </x:c>
       <x:c r="B68" s="19" t="str">
         <x:v>玄关</x:v>
       </x:c>
       <x:c r="C68" s="19" t="str">
+        <x:v>收纳</x:v>
+      </x:c>
+      <x:c r="D68" s="19" t="str">
+        <x:v>随手置物台面</x:v>
+      </x:c>
+      <x:c r="E68" s="19" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F68" s="22" t="str">
+        <x:v>需要 / 不需要</x:v>
+      </x:c>
+      <x:c r="G68" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H68" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I68" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J68" s="22" t="str">
+        <x:v>钥匙、快递临时放置</x:v>
+      </x:c>
+      <x:c r="K68" s="19" t="str">
+        <x:v>S5</x:v>
+      </x:c>
+      <x:c r="L68" s="22" t="str"/>
+    </x:row>
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
+      <x:c r="A69" s="19" t="str">
+        <x:v>ex_other</x:v>
+      </x:c>
+      <x:c r="B69" s="19" t="str">
+        <x:v>玄关</x:v>
+      </x:c>
+      <x:c r="C69" s="19" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="D68" s="19" t="str">
+      <x:c r="D69" s="19" t="str">
         <x:v>其他需求</x:v>
       </x:c>
-      <x:c r="E68" s="19" t="str">
+      <x:c r="E69" s="19" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F68" s="22" t="str">
+      <x:c r="F69" s="22" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G68" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H68" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I68" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J68" s="22" t="str">
+      <x:c r="G69" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H69" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I69" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J69" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K68" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L68" s="22" t="str"/>
-    </x:row>
-    <x:row r="69" ht="24" hidden="0" customHeight="1">
-      <x:c r="A69" s="27" t="str">
+      <x:c r="K69" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L69" s="22" t="str"/>
+    </x:row>
+    <x:row r="70" ht="24" hidden="0" customHeight="1">
+      <x:c r="A70" s="27" t="str">
         <x:v>lv_type</x:v>
       </x:c>
-      <x:c r="B69" s="27" t="str">
+      <x:c r="B70" s="27" t="str">
         <x:v>客厅</x:v>
       </x:c>
-      <x:c r="C69" s="27" t="str">
+      <x:c r="C70" s="27" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="D69" s="27" t="str">
+      <x:c r="D70" s="27" t="str">
         <x:v>客厅类型</x:v>
       </x:c>
-      <x:c r="E69" s="27" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F69" s="28" t="str">
+      <x:c r="E70" s="27" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F70" s="28" t="str">
         <x:v>简约型 / 储物型</x:v>
       </x:c>
-      <x:c r="G69" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H69" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I69" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J69" s="28" t="str">
+      <x:c r="G70" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H70" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I70" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J70" s="28" t="str">
         <x:v>储物量评估</x:v>
       </x:c>
-      <x:c r="K69" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L69" s="28" t="str"/>
-    </x:row>
-    <x:row r="70" ht="48" hidden="0" customHeight="1">
-      <x:c r="A70" s="19" t="str">
+      <x:c r="K70" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L70" s="28" t="str"/>
+    </x:row>
+    <x:row r="71" ht="48" hidden="0" customHeight="1">
+      <x:c r="A71" s="19" t="str">
         <x:v>lv_core</x:v>
-      </x:c>
-      <x:c r="B70" s="19" t="str">
-        <x:v>客厅</x:v>
-      </x:c>
-      <x:c r="C70" s="19" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D70" s="19" t="str">
-        <x:v>核心功能</x:v>
-      </x:c>
-      <x:c r="E70" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F70" s="22" t="str">
-        <x:v>会客为主 / 家人休闲 / 亲子活动 / 学习阅读</x:v>
-      </x:c>
-      <x:c r="G70" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H70" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I70" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J70" s="22" t="str">
-        <x:v>布局与家具建议</x:v>
-      </x:c>
-      <x:c r="K70" s="19" t="str">
-        <x:v>S4</x:v>
-      </x:c>
-      <x:c r="L70" s="22" t="str"/>
-    </x:row>
-    <x:row r="71" ht="36" hidden="0" customHeight="1">
-      <x:c r="A71" s="19" t="str">
-        <x:v>lv_screen</x:v>
       </x:c>
       <x:c r="B71" s="19" t="str">
         <x:v>客厅</x:v>
       </x:c>
       <x:c r="C71" s="19" t="str">
-        <x:v>影音</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="D71" s="19" t="str">
-        <x:v>电视或投影</x:v>
+        <x:v>核心功能</x:v>
       </x:c>
       <x:c r="E71" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F71" s="22" t="str">
-        <x:v>电视 / 投影 / 都不需要</x:v>
+        <x:v>会客为主 / 家人休闲 / 亲子活动 / 学习阅读</x:v>
       </x:c>
       <x:c r="G71" s="25" t="str">
         <x:v>选填</x:v>
@@ -2918,16 +2920,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J71" s="22" t="str">
-        <x:v>背景墙、线路与插座</x:v>
+        <x:v>布局与家具建议</x:v>
       </x:c>
       <x:c r="K71" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>S4</x:v>
       </x:c>
       <x:c r="L71" s="22" t="str"/>
     </x:row>
-    <x:row r="72" ht="24" hidden="0" customHeight="1">
+    <x:row r="72" ht="36" hidden="0" customHeight="1">
       <x:c r="A72" s="19" t="str">
-        <x:v>lv_wall</x:v>
+        <x:v>lv_screen</x:v>
       </x:c>
       <x:c r="B72" s="19" t="str">
         <x:v>客厅</x:v>
@@ -2936,13 +2938,13 @@
         <x:v>影音</x:v>
       </x:c>
       <x:c r="D72" s="19" t="str">
-        <x:v>背景墙</x:v>
+        <x:v>电视或投影</x:v>
       </x:c>
       <x:c r="E72" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F72" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>电视 / 投影 / 都不需要</x:v>
       </x:c>
       <x:c r="G72" s="25" t="str">
         <x:v>选填</x:v>
@@ -2954,16 +2956,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J72" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>背景墙、线路与插座</x:v>
       </x:c>
       <x:c r="K72" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L72" s="22" t="str"/>
     </x:row>
     <x:row r="73" ht="24" hidden="0" customHeight="1">
       <x:c r="A73" s="19" t="str">
-        <x:v>lv_tv_cabinet</x:v>
+        <x:v>lv_wall</x:v>
       </x:c>
       <x:c r="B73" s="19" t="str">
         <x:v>客厅</x:v>
@@ -2972,7 +2974,7 @@
         <x:v>影音</x:v>
       </x:c>
       <x:c r="D73" s="19" t="str">
-        <x:v>电视柜</x:v>
+        <x:v>背景墙</x:v>
       </x:c>
       <x:c r="E73" s="19" t="str">
         <x:v>单选</x:v>
@@ -2999,16 +3001,16 @@
     </x:row>
     <x:row r="74" ht="24" hidden="0" customHeight="1">
       <x:c r="A74" s="19" t="str">
-        <x:v>lv_bookshelf</x:v>
+        <x:v>lv_tv_cabinet</x:v>
       </x:c>
       <x:c r="B74" s="19" t="str">
         <x:v>客厅</x:v>
       </x:c>
       <x:c r="C74" s="19" t="str">
-        <x:v>功能</x:v>
+        <x:v>影音</x:v>
       </x:c>
       <x:c r="D74" s="19" t="str">
-        <x:v>书墙或大长桌</x:v>
+        <x:v>电视柜</x:v>
       </x:c>
       <x:c r="E74" s="19" t="str">
         <x:v>单选</x:v>
@@ -3026,16 +3028,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J74" s="22" t="str">
-        <x:v>学习型客厅布局</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K74" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L74" s="22" t="str"/>
     </x:row>
     <x:row r="75" ht="24" hidden="0" customHeight="1">
       <x:c r="A75" s="19" t="str">
-        <x:v>lv_snack</x:v>
+        <x:v>lv_bookshelf</x:v>
       </x:c>
       <x:c r="B75" s="19" t="str">
         <x:v>客厅</x:v>
@@ -3044,7 +3046,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D75" s="19" t="str">
-        <x:v>零食柜</x:v>
+        <x:v>书墙或大长桌</x:v>
       </x:c>
       <x:c r="E75" s="19" t="str">
         <x:v>单选</x:v>
@@ -3062,16 +3064,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J75" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>学习型客厅布局</x:v>
       </x:c>
       <x:c r="K75" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>S4</x:v>
       </x:c>
       <x:c r="L75" s="22" t="str"/>
     </x:row>
     <x:row r="76" ht="24" hidden="0" customHeight="1">
       <x:c r="A76" s="19" t="str">
-        <x:v>lv_piano</x:v>
+        <x:v>lv_snack</x:v>
       </x:c>
       <x:c r="B76" s="19" t="str">
         <x:v>客厅</x:v>
@@ -3080,7 +3082,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D76" s="19" t="str">
-        <x:v>钢琴放置</x:v>
+        <x:v>零食柜</x:v>
       </x:c>
       <x:c r="E76" s="19" t="str">
         <x:v>单选</x:v>
@@ -3098,16 +3100,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J76" s="22" t="str">
-        <x:v>承重与隔音</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K76" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L76" s="22" t="str"/>
     </x:row>
     <x:row r="77" ht="24" hidden="0" customHeight="1">
       <x:c r="A77" s="19" t="str">
-        <x:v>lv_fitness</x:v>
+        <x:v>lv_piano</x:v>
       </x:c>
       <x:c r="B77" s="19" t="str">
         <x:v>客厅</x:v>
@@ -3116,7 +3118,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D77" s="19" t="str">
-        <x:v>健身器材</x:v>
+        <x:v>钢琴放置</x:v>
       </x:c>
       <x:c r="E77" s="19" t="str">
         <x:v>单选</x:v>
@@ -3134,16 +3136,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J77" s="22" t="str">
-        <x:v>地面承重与电源</x:v>
+        <x:v>承重与隔音</x:v>
       </x:c>
       <x:c r="K77" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L77" s="22" t="str"/>
     </x:row>
-    <x:row r="78" ht="36" hidden="0" customHeight="1">
+    <x:row r="78" ht="24" hidden="0" customHeight="1">
       <x:c r="A78" s="19" t="str">
-        <x:v>lv_play</x:v>
+        <x:v>lv_fitness</x:v>
       </x:c>
       <x:c r="B78" s="19" t="str">
         <x:v>客厅</x:v>
@@ -3152,7 +3154,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D78" s="19" t="str">
-        <x:v>儿童活动或手工区</x:v>
+        <x:v>健身器材</x:v>
       </x:c>
       <x:c r="E78" s="19" t="str">
         <x:v>单选</x:v>
@@ -3170,31 +3172,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J78" s="22" t="str">
-        <x:v>活动空间与作品展示墙</x:v>
+        <x:v>地面承重与电源</x:v>
       </x:c>
       <x:c r="K78" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L78" s="22" t="str"/>
     </x:row>
-    <x:row r="79" ht="48" hidden="0" customHeight="1">
+    <x:row r="79" ht="36" hidden="0" customHeight="1">
       <x:c r="A79" s="19" t="str">
-        <x:v>lv_sofa</x:v>
+        <x:v>lv_play</x:v>
       </x:c>
       <x:c r="B79" s="19" t="str">
         <x:v>客厅</x:v>
       </x:c>
       <x:c r="C79" s="19" t="str">
-        <x:v>家具</x:v>
+        <x:v>功能</x:v>
       </x:c>
       <x:c r="D79" s="19" t="str">
-        <x:v>沙发形式</x:v>
+        <x:v>儿童活动或手工区</x:v>
       </x:c>
       <x:c r="E79" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F79" s="22" t="str">
-        <x:v>传统沙发 / 灵活家具 / 地台软垫 / 沙发床</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G79" s="25" t="str">
         <x:v>选填</x:v>
@@ -3206,139 +3208,139 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J79" s="22" t="str">
-        <x:v>空间灵活性</x:v>
+        <x:v>活动空间与作品展示墙</x:v>
       </x:c>
       <x:c r="K79" s="19" t="str">
         <x:v>S5</x:v>
       </x:c>
       <x:c r="L79" s="22" t="str"/>
     </x:row>
-    <x:row r="80" ht="15" hidden="0" customHeight="1">
+    <x:row r="80" ht="48" hidden="0" customHeight="1">
       <x:c r="A80" s="19" t="str">
-        <x:v>lv_other</x:v>
+        <x:v>lv_sofa</x:v>
       </x:c>
       <x:c r="B80" s="19" t="str">
         <x:v>客厅</x:v>
       </x:c>
       <x:c r="C80" s="19" t="str">
+        <x:v>家具</x:v>
+      </x:c>
+      <x:c r="D80" s="19" t="str">
+        <x:v>沙发形式</x:v>
+      </x:c>
+      <x:c r="E80" s="19" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F80" s="22" t="str">
+        <x:v>传统沙发 / 灵活家具 / 地台软垫 / 沙发床</x:v>
+      </x:c>
+      <x:c r="G80" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H80" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I80" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J80" s="22" t="str">
+        <x:v>空间灵活性</x:v>
+      </x:c>
+      <x:c r="K80" s="19" t="str">
+        <x:v>S5</x:v>
+      </x:c>
+      <x:c r="L80" s="22" t="str"/>
+    </x:row>
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
+      <x:c r="A81" s="19" t="str">
+        <x:v>lv_other</x:v>
+      </x:c>
+      <x:c r="B81" s="19" t="str">
+        <x:v>客厅</x:v>
+      </x:c>
+      <x:c r="C81" s="19" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="D80" s="19" t="str">
+      <x:c r="D81" s="19" t="str">
         <x:v>其他需求</x:v>
       </x:c>
-      <x:c r="E80" s="19" t="str">
+      <x:c r="E81" s="19" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F80" s="22" t="str">
+      <x:c r="F81" s="22" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G80" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H80" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I80" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J80" s="22" t="str">
+      <x:c r="G81" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H81" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I81" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J81" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K80" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L80" s="22" t="str"/>
-    </x:row>
-    <x:row r="81" ht="15" hidden="0" customHeight="1">
-      <x:c r="A81" s="27" t="str">
+      <x:c r="K81" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L81" s="22" t="str"/>
+    </x:row>
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
+      <x:c r="A82" s="27" t="str">
         <x:v>dn_people</x:v>
       </x:c>
-      <x:c r="B81" s="27" t="str">
+      <x:c r="B82" s="27" t="str">
         <x:v>餐厅</x:v>
       </x:c>
-      <x:c r="C81" s="27" t="str">
+      <x:c r="C82" s="27" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="D81" s="27" t="str">
+      <x:c r="D82" s="27" t="str">
         <x:v>日常用餐人数</x:v>
       </x:c>
-      <x:c r="E81" s="27" t="str">
+      <x:c r="E82" s="27" t="str">
         <x:v>数字</x:v>
       </x:c>
-      <x:c r="F81" s="28" t="str">
+      <x:c r="F82" s="28" t="str">
         <x:v>人</x:v>
       </x:c>
-      <x:c r="G81" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H81" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I81" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J81" s="28" t="str">
+      <x:c r="G82" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H82" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I82" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J82" s="28" t="str">
         <x:v>餐桌尺寸</x:v>
       </x:c>
-      <x:c r="K81" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L81" s="28" t="str"/>
-    </x:row>
-    <x:row r="82" ht="60" hidden="0" customHeight="1">
-      <x:c r="A82" s="19" t="str">
+      <x:c r="K82" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L82" s="28" t="str"/>
+    </x:row>
+    <x:row r="83" ht="60" hidden="0" customHeight="1">
+      <x:c r="A83" s="19" t="str">
         <x:v>dn_table</x:v>
-      </x:c>
-      <x:c r="B82" s="19" t="str">
-        <x:v>餐厅</x:v>
-      </x:c>
-      <x:c r="C82" s="19" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D82" s="19" t="str">
-        <x:v>餐桌形式</x:v>
-      </x:c>
-      <x:c r="E82" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F82" s="22" t="str">
-        <x:v>圆桌 / 方桌 / 岛台餐桌结合 / 其他</x:v>
-      </x:c>
-      <x:c r="G82" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H82" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I82" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J82" s="22" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="K82" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L82" s="22" t="str"/>
-    </x:row>
-    <x:row r="83" ht="48" hidden="0" customHeight="1">
-      <x:c r="A83" s="19" t="str">
-        <x:v>dn_cabinet</x:v>
       </x:c>
       <x:c r="B83" s="19" t="str">
         <x:v>餐厅</x:v>
       </x:c>
       <x:c r="C83" s="19" t="str">
-        <x:v>收纳</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="D83" s="19" t="str">
-        <x:v>餐厅柜子</x:v>
+        <x:v>餐桌形式</x:v>
       </x:c>
       <x:c r="E83" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F83" s="22" t="str">
-        <x:v>餐边柜 / 酒柜 / 装饰柜 / 其他</x:v>
+        <x:v>圆桌 / 方桌 / 岛台餐桌结合 / 其他</x:v>
       </x:c>
       <x:c r="G83" s="25" t="str">
         <x:v>选填</x:v>
@@ -3357,24 +3359,24 @@
       </x:c>
       <x:c r="L83" s="22" t="str"/>
     </x:row>
-    <x:row r="84" ht="24" hidden="0" customHeight="1">
+    <x:row r="84" ht="48" hidden="0" customHeight="1">
       <x:c r="A84" s="19" t="str">
-        <x:v>dn_coffee</x:v>
+        <x:v>dn_cabinet</x:v>
       </x:c>
       <x:c r="B84" s="19" t="str">
         <x:v>餐厅</x:v>
       </x:c>
       <x:c r="C84" s="19" t="str">
-        <x:v>功能</x:v>
+        <x:v>收纳</x:v>
       </x:c>
       <x:c r="D84" s="19" t="str">
-        <x:v>咖啡机</x:v>
+        <x:v>餐厅柜子</x:v>
       </x:c>
       <x:c r="E84" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F84" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>餐边柜 / 酒柜 / 装饰柜 / 其他</x:v>
       </x:c>
       <x:c r="G84" s="25" t="str">
         <x:v>选填</x:v>
@@ -3386,16 +3388,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J84" s="22" t="str">
-        <x:v>台面空间与插座</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K84" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L84" s="22" t="str"/>
     </x:row>
-    <x:row r="85" ht="15" hidden="0" customHeight="1">
+    <x:row r="85" ht="24" hidden="0" customHeight="1">
       <x:c r="A85" s="19" t="str">
-        <x:v>dn_bar</x:v>
+        <x:v>dn_coffee</x:v>
       </x:c>
       <x:c r="B85" s="19" t="str">
         <x:v>餐厅</x:v>
@@ -3404,7 +3406,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D85" s="19" t="str">
-        <x:v>吧台</x:v>
+        <x:v>咖啡机</x:v>
       </x:c>
       <x:c r="E85" s="19" t="str">
         <x:v>单选</x:v>
@@ -3422,16 +3424,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J85" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>台面空间与插座</x:v>
       </x:c>
       <x:c r="K85" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L85" s="22" t="str"/>
     </x:row>
-    <x:row r="86" ht="24" hidden="0" customHeight="1">
+    <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="19" t="str">
-        <x:v>dn_work</x:v>
+        <x:v>dn_bar</x:v>
       </x:c>
       <x:c r="B86" s="19" t="str">
         <x:v>餐厅</x:v>
@@ -3440,7 +3442,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D86" s="19" t="str">
-        <x:v>是否在餐桌办公或写作业</x:v>
+        <x:v>吧台</x:v>
       </x:c>
       <x:c r="E86" s="19" t="str">
         <x:v>单选</x:v>
@@ -3458,16 +3460,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J86" s="22" t="str">
-        <x:v>吊灯位置与插座</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K86" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L86" s="22" t="str"/>
     </x:row>
-    <x:row r="87" ht="15" hidden="0" customHeight="1">
+    <x:row r="87" ht="24" hidden="0" customHeight="1">
       <x:c r="A87" s="19" t="str">
-        <x:v>dn_fan</x:v>
+        <x:v>dn_work</x:v>
       </x:c>
       <x:c r="B87" s="19" t="str">
         <x:v>餐厅</x:v>
@@ -3476,7 +3478,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D87" s="19" t="str">
-        <x:v>吊扇灯</x:v>
+        <x:v>是否在餐桌办公或写作业</x:v>
       </x:c>
       <x:c r="E87" s="19" t="str">
         <x:v>单选</x:v>
@@ -3494,16 +3496,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J87" s="22" t="str">
-        <x:v>顶面电路</x:v>
+        <x:v>吊灯位置与插座</x:v>
       </x:c>
       <x:c r="K87" s="19" t="str">
         <x:v>S3</x:v>
       </x:c>
       <x:c r="L87" s="22" t="str"/>
     </x:row>
-    <x:row r="88" ht="36" hidden="0" customHeight="1">
+    <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="19" t="str">
-        <x:v>dn_party</x:v>
+        <x:v>dn_fan</x:v>
       </x:c>
       <x:c r="B88" s="19" t="str">
         <x:v>餐厅</x:v>
@@ -3512,13 +3514,13 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D88" s="19" t="str">
-        <x:v>聚会或派对需求</x:v>
+        <x:v>吊扇灯</x:v>
       </x:c>
       <x:c r="E88" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F88" s="22" t="str">
-        <x:v>经常 / 偶尔 / 无</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G88" s="25" t="str">
         <x:v>选填</x:v>
@@ -3530,142 +3532,142 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J88" s="22" t="str">
-        <x:v>餐桌可扩展性与动线</x:v>
+        <x:v>顶面电路</x:v>
       </x:c>
       <x:c r="K88" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L88" s="22" t="str"/>
     </x:row>
-    <x:row r="89" ht="15" hidden="0" customHeight="1">
+    <x:row r="89" ht="36" hidden="0" customHeight="1">
       <x:c r="A89" s="19" t="str">
-        <x:v>dn_other</x:v>
+        <x:v>dn_party</x:v>
       </x:c>
       <x:c r="B89" s="19" t="str">
         <x:v>餐厅</x:v>
       </x:c>
       <x:c r="C89" s="19" t="str">
+        <x:v>功能</x:v>
+      </x:c>
+      <x:c r="D89" s="19" t="str">
+        <x:v>聚会或派对需求</x:v>
+      </x:c>
+      <x:c r="E89" s="19" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F89" s="22" t="str">
+        <x:v>经常 / 偶尔 / 无</x:v>
+      </x:c>
+      <x:c r="G89" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H89" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I89" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J89" s="22" t="str">
+        <x:v>餐桌可扩展性与动线</x:v>
+      </x:c>
+      <x:c r="K89" s="19" t="str">
+        <x:v>S5</x:v>
+      </x:c>
+      <x:c r="L89" s="22" t="str"/>
+    </x:row>
+    <x:row r="90" ht="15" hidden="0" customHeight="1">
+      <x:c r="A90" s="19" t="str">
+        <x:v>dn_other</x:v>
+      </x:c>
+      <x:c r="B90" s="19" t="str">
+        <x:v>餐厅</x:v>
+      </x:c>
+      <x:c r="C90" s="19" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="D89" s="19" t="str">
+      <x:c r="D90" s="19" t="str">
         <x:v>其他需求</x:v>
       </x:c>
-      <x:c r="E89" s="19" t="str">
+      <x:c r="E90" s="19" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F89" s="22" t="str">
+      <x:c r="F90" s="22" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G89" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H89" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I89" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J89" s="22" t="str">
+      <x:c r="G90" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H90" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I90" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J90" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K89" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L89" s="22" t="str"/>
-    </x:row>
-    <x:row r="90" ht="15" hidden="0" customHeight="1">
-      <x:c r="A90" s="27" t="str">
+      <x:c r="K90" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L90" s="22" t="str"/>
+    </x:row>
+    <x:row r="91" ht="15" hidden="0" customHeight="1">
+      <x:c r="A91" s="27" t="str">
         <x:v>kt_height_m</x:v>
       </x:c>
-      <x:c r="B90" s="27" t="str">
+      <x:c r="B91" s="27" t="str">
         <x:v>厨房</x:v>
       </x:c>
-      <x:c r="C90" s="27" t="str">
+      <x:c r="C91" s="27" t="str">
         <x:v>身高</x:v>
       </x:c>
-      <x:c r="D90" s="27" t="str">
+      <x:c r="D91" s="27" t="str">
         <x:v>男主人身高</x:v>
       </x:c>
-      <x:c r="E90" s="27" t="str">
+      <x:c r="E91" s="27" t="str">
         <x:v>数字</x:v>
       </x:c>
-      <x:c r="F90" s="28" t="str">
+      <x:c r="F91" s="28" t="str">
         <x:v>cm</x:v>
       </x:c>
-      <x:c r="G90" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H90" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I90" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J90" s="28" t="str">
+      <x:c r="G91" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H91" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I91" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J91" s="28" t="str">
         <x:v>台面高度</x:v>
       </x:c>
-      <x:c r="K90" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L90" s="28" t="str"/>
-    </x:row>
-    <x:row r="91" ht="15" hidden="0" customHeight="1">
-      <x:c r="A91" s="19" t="str">
+      <x:c r="K91" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L91" s="28" t="str"/>
+    </x:row>
+    <x:row r="92" ht="15" hidden="0" customHeight="1">
+      <x:c r="A92" s="19" t="str">
         <x:v>kt_height_f</x:v>
-      </x:c>
-      <x:c r="B91" s="19" t="str">
-        <x:v>厨房</x:v>
-      </x:c>
-      <x:c r="C91" s="19" t="str">
-        <x:v>身高</x:v>
-      </x:c>
-      <x:c r="D91" s="19" t="str">
-        <x:v>女主人身高</x:v>
-      </x:c>
-      <x:c r="E91" s="19" t="str">
-        <x:v>数字</x:v>
-      </x:c>
-      <x:c r="F91" s="22" t="str">
-        <x:v>cm</x:v>
-      </x:c>
-      <x:c r="G91" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H91" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I91" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J91" s="22" t="str">
-        <x:v>台面高度</x:v>
-      </x:c>
-      <x:c r="K91" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L91" s="22" t="str"/>
-    </x:row>
-    <x:row r="92" ht="48" hidden="0" customHeight="1">
-      <x:c r="A92" s="19" t="str">
-        <x:v>kt_freq</x:v>
       </x:c>
       <x:c r="B92" s="19" t="str">
         <x:v>厨房</x:v>
       </x:c>
       <x:c r="C92" s="19" t="str">
-        <x:v>使用习惯</x:v>
+        <x:v>身高</x:v>
       </x:c>
       <x:c r="D92" s="19" t="str">
-        <x:v>下厨频率</x:v>
+        <x:v>女主人身高</x:v>
       </x:c>
       <x:c r="E92" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>数字</x:v>
       </x:c>
       <x:c r="F92" s="22" t="str">
-        <x:v>基本不 / 偶尔 / 经常</x:v>
+        <x:v>cm</x:v>
       </x:c>
       <x:c r="G92" s="25" t="str">
-        <x:v>推荐填写</x:v>
+        <x:v>选填</x:v>
       </x:c>
       <x:c r="H92" s="25" t="str">
         <x:v>固定</x:v>
@@ -3674,7 +3676,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J92" s="22" t="str">
-        <x:v>开放厨房油烟方案、设备配置</x:v>
+        <x:v>台面高度</x:v>
       </x:c>
       <x:c r="K92" s="19" t="str">
         <x:v>原件</x:v>
@@ -3683,7 +3685,7 @@
     </x:row>
     <x:row r="93" ht="48" hidden="0" customHeight="1">
       <x:c r="A93" s="19" t="str">
-        <x:v>kt_cooker</x:v>
+        <x:v>kt_freq</x:v>
       </x:c>
       <x:c r="B93" s="19" t="str">
         <x:v>厨房</x:v>
@@ -3692,16 +3694,16 @@
         <x:v>使用习惯</x:v>
       </x:c>
       <x:c r="D93" s="19" t="str">
-        <x:v>主要做饭人</x:v>
+        <x:v>下厨频率</x:v>
       </x:c>
       <x:c r="E93" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F93" s="22" t="str">
-        <x:v>男主人 / 女主人 / 父母 / 保姆</x:v>
+        <x:v>基本不 / 偶尔 / 经常</x:v>
       </x:c>
       <x:c r="G93" s="25" t="str">
-        <x:v>选填</x:v>
+        <x:v>推荐填写</x:v>
       </x:c>
       <x:c r="H93" s="25" t="str">
         <x:v>固定</x:v>
@@ -3710,16 +3712,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J93" s="22" t="str">
-        <x:v>台面高度与动线</x:v>
+        <x:v>开放厨房油烟方案、设备配置</x:v>
       </x:c>
       <x:c r="K93" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L93" s="22" t="str"/>
     </x:row>
-    <x:row r="94" ht="15" hidden="0" customHeight="1">
+    <x:row r="94" ht="48" hidden="0" customHeight="1">
       <x:c r="A94" s="19" t="str">
-        <x:v>kt_cooker_h</x:v>
+        <x:v>kt_cooker</x:v>
       </x:c>
       <x:c r="B94" s="19" t="str">
         <x:v>厨房</x:v>
@@ -3728,13 +3730,13 @@
         <x:v>使用习惯</x:v>
       </x:c>
       <x:c r="D94" s="19" t="str">
-        <x:v>其他做饭人身高</x:v>
+        <x:v>主要做饭人</x:v>
       </x:c>
       <x:c r="E94" s="19" t="str">
-        <x:v>数字</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F94" s="22" t="str">
-        <x:v>cm</x:v>
+        <x:v>男主人 / 女主人 / 父母 / 保姆</x:v>
       </x:c>
       <x:c r="G94" s="25" t="str">
         <x:v>选填</x:v>
@@ -3746,16 +3748,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J94" s="22" t="str">
-        <x:v>台面高度</x:v>
+        <x:v>台面高度与动线</x:v>
       </x:c>
       <x:c r="K94" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L94" s="22" t="str"/>
     </x:row>
-    <x:row r="95" ht="36" hidden="0" customHeight="1">
+    <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="19" t="str">
-        <x:v>kt_cuisine</x:v>
+        <x:v>kt_cooker_h</x:v>
       </x:c>
       <x:c r="B95" s="19" t="str">
         <x:v>厨房</x:v>
@@ -3764,13 +3766,13 @@
         <x:v>使用习惯</x:v>
       </x:c>
       <x:c r="D95" s="19" t="str">
-        <x:v>菜系偏好</x:v>
+        <x:v>其他做饭人身高</x:v>
       </x:c>
       <x:c r="E95" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>数字</x:v>
       </x:c>
       <x:c r="F95" s="22" t="str">
-        <x:v>中餐为主 / 中西结合 / 西餐为主</x:v>
+        <x:v>cm</x:v>
       </x:c>
       <x:c r="G95" s="25" t="str">
         <x:v>选填</x:v>
@@ -3782,34 +3784,34 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J95" s="22" t="str">
-        <x:v>油烟机风量与灶具</x:v>
+        <x:v>台面高度</x:v>
       </x:c>
       <x:c r="K95" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L95" s="22" t="str"/>
     </x:row>
     <x:row r="96" ht="36" hidden="0" customHeight="1">
       <x:c r="A96" s="19" t="str">
-        <x:v>kt_form</x:v>
+        <x:v>kt_cuisine</x:v>
       </x:c>
       <x:c r="B96" s="19" t="str">
         <x:v>厨房</x:v>
       </x:c>
       <x:c r="C96" s="19" t="str">
-        <x:v>形式</x:v>
+        <x:v>使用习惯</x:v>
       </x:c>
       <x:c r="D96" s="19" t="str">
-        <x:v>厨房形式</x:v>
+        <x:v>菜系偏好</x:v>
       </x:c>
       <x:c r="E96" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F96" s="22" t="str">
-        <x:v>开放式 / 半开放式 / 封闭式</x:v>
+        <x:v>中餐为主 / 中西结合 / 西餐为主</x:v>
       </x:c>
       <x:c r="G96" s="25" t="str">
-        <x:v>推荐填写</x:v>
+        <x:v>选填</x:v>
       </x:c>
       <x:c r="H96" s="25" t="str">
         <x:v>固定</x:v>
@@ -3818,16 +3820,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J96" s="22" t="str">
-        <x:v>油烟与燃气备案</x:v>
+        <x:v>油烟机风量与灶具</x:v>
       </x:c>
       <x:c r="K96" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S4</x:v>
       </x:c>
       <x:c r="L96" s="22" t="str"/>
     </x:row>
     <x:row r="97" ht="36" hidden="0" customHeight="1">
       <x:c r="A97" s="19" t="str">
-        <x:v>kt_door</x:v>
+        <x:v>kt_form</x:v>
       </x:c>
       <x:c r="B97" s="19" t="str">
         <x:v>厨房</x:v>
@@ -3836,13 +3838,13 @@
         <x:v>形式</x:v>
       </x:c>
       <x:c r="D97" s="19" t="str">
-        <x:v>厨房门形式</x:v>
+        <x:v>厨房形式</x:v>
       </x:c>
       <x:c r="E97" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F97" s="22" t="str">
-        <x:v>推拉门 / 平开门 / 无门</x:v>
+        <x:v>开放式 / 半开放式 / 封闭式</x:v>
       </x:c>
       <x:c r="G97" s="25" t="str">
         <x:v>选填</x:v>
@@ -3854,31 +3856,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J97" s="22" t="str">
-        <x:v>动线优化</x:v>
+        <x:v>油烟与燃气备案</x:v>
       </x:c>
       <x:c r="K97" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L97" s="22" t="str"/>
     </x:row>
     <x:row r="98" ht="36" hidden="0" customHeight="1">
       <x:c r="A98" s="19" t="str">
-        <x:v>kt_hood</x:v>
+        <x:v>kt_door</x:v>
       </x:c>
       <x:c r="B98" s="19" t="str">
         <x:v>厨房</x:v>
       </x:c>
       <x:c r="C98" s="19" t="str">
-        <x:v>设备</x:v>
+        <x:v>形式</x:v>
       </x:c>
       <x:c r="D98" s="19" t="str">
-        <x:v>油烟机形式</x:v>
+        <x:v>厨房门形式</x:v>
       </x:c>
       <x:c r="E98" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F98" s="22" t="str">
-        <x:v>侧吸 / 顶吸 / 集成灶</x:v>
+        <x:v>推拉门 / 平开门 / 无门</x:v>
       </x:c>
       <x:c r="G98" s="25" t="str">
         <x:v>选填</x:v>
@@ -3890,16 +3892,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J98" s="22" t="str">
-        <x:v>吊柜与排烟方式</x:v>
+        <x:v>动线优化</x:v>
       </x:c>
       <x:c r="K98" s="19" t="str">
         <x:v>S5</x:v>
       </x:c>
       <x:c r="L98" s="22" t="str"/>
     </x:row>
-    <x:row r="99" ht="24" hidden="0" customHeight="1">
+    <x:row r="99" ht="36" hidden="0" customHeight="1">
       <x:c r="A99" s="19" t="str">
-        <x:v>kt_sink</x:v>
+        <x:v>kt_hood</x:v>
       </x:c>
       <x:c r="B99" s="19" t="str">
         <x:v>厨房</x:v>
@@ -3908,13 +3910,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D99" s="19" t="str">
-        <x:v>水槽形式</x:v>
+        <x:v>油烟机形式</x:v>
       </x:c>
       <x:c r="E99" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F99" s="22" t="str">
-        <x:v>大单槽 / 双槽</x:v>
+        <x:v>侧吸 / 顶吸 / 集成灶</x:v>
       </x:c>
       <x:c r="G99" s="25" t="str">
         <x:v>选填</x:v>
@@ -3926,16 +3928,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J99" s="22" t="str">
-        <x:v>台面与洗碗机匹配</x:v>
+        <x:v>吊柜与排烟方式</x:v>
       </x:c>
       <x:c r="K99" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L99" s="22" t="str"/>
     </x:row>
-    <x:row r="100" ht="36" hidden="0" customHeight="1">
+    <x:row r="100" ht="24" hidden="0" customHeight="1">
       <x:c r="A100" s="19" t="str">
-        <x:v>kt_counter</x:v>
+        <x:v>kt_sink</x:v>
       </x:c>
       <x:c r="B100" s="19" t="str">
         <x:v>厨房</x:v>
@@ -3944,13 +3946,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D100" s="19" t="str">
-        <x:v>高低台面</x:v>
+        <x:v>水槽形式</x:v>
       </x:c>
       <x:c r="E100" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F100" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>大单槽 / 双槽</x:v>
       </x:c>
       <x:c r="G100" s="25" t="str">
         <x:v>选填</x:v>
@@ -3962,7 +3964,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J100" s="22" t="str">
-        <x:v>洗切与烹饪台面高度差</x:v>
+        <x:v>台面与洗碗机匹配</x:v>
       </x:c>
       <x:c r="K100" s="19" t="str">
         <x:v>S3</x:v>
@@ -3971,7 +3973,7 @@
     </x:row>
     <x:row r="101" ht="36" hidden="0" customHeight="1">
       <x:c r="A101" s="19" t="str">
-        <x:v>kt_dishwasher</x:v>
+        <x:v>kt_counter</x:v>
       </x:c>
       <x:c r="B101" s="19" t="str">
         <x:v>厨房</x:v>
@@ -3980,13 +3982,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D101" s="19" t="str">
-        <x:v>洗碗机</x:v>
+        <x:v>高低台面</x:v>
       </x:c>
       <x:c r="E101" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F101" s="22" t="str">
-        <x:v>前开式 / 水槽式 / 不需要</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G101" s="25" t="str">
         <x:v>选填</x:v>
@@ -3998,16 +4000,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J101" s="22" t="str">
-        <x:v>水电与橱柜尺寸</x:v>
+        <x:v>洗切与烹饪台面高度差</x:v>
       </x:c>
       <x:c r="K101" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L101" s="22" t="str"/>
     </x:row>
-    <x:row r="102" ht="60" hidden="0" customHeight="1">
+    <x:row r="102" ht="36" hidden="0" customHeight="1">
       <x:c r="A102" s="19" t="str">
-        <x:v>kt_fridge</x:v>
+        <x:v>kt_dishwasher</x:v>
       </x:c>
       <x:c r="B102" s="19" t="str">
         <x:v>厨房</x:v>
@@ -4016,13 +4018,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D102" s="19" t="str">
-        <x:v>冰箱形式</x:v>
+        <x:v>洗碗机</x:v>
       </x:c>
       <x:c r="E102" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F102" s="22" t="str">
-        <x:v>内嵌 / 非内嵌 / 单开 / 多开 / 大双开</x:v>
+        <x:v>前开式 / 水槽式 / 不需要</x:v>
       </x:c>
       <x:c r="G102" s="25" t="str">
         <x:v>选填</x:v>
@@ -4034,16 +4036,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J102" s="22" t="str">
-        <x:v>橱柜与电源位置</x:v>
+        <x:v>水电与橱柜尺寸</x:v>
       </x:c>
       <x:c r="K102" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L102" s="22" t="str"/>
     </x:row>
-    <x:row r="103" ht="24" hidden="0" customHeight="1">
+    <x:row r="103" ht="60" hidden="0" customHeight="1">
       <x:c r="A103" s="19" t="str">
-        <x:v>kt_freezer</x:v>
+        <x:v>kt_fridge</x:v>
       </x:c>
       <x:c r="B103" s="19" t="str">
         <x:v>厨房</x:v>
@@ -4052,13 +4054,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D103" s="19" t="str">
-        <x:v>是否需要冰柜</x:v>
+        <x:v>冰箱形式</x:v>
       </x:c>
       <x:c r="E103" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F103" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>内嵌 / 非内嵌 / 单开 / 多开 / 大双开</x:v>
       </x:c>
       <x:c r="G103" s="25" t="str">
         <x:v>选填</x:v>
@@ -4070,16 +4072,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J103" s="22" t="str">
-        <x:v>位置与电源预留</x:v>
+        <x:v>橱柜与电源位置</x:v>
       </x:c>
       <x:c r="K103" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L103" s="22" t="str"/>
     </x:row>
-    <x:row r="104" ht="120" hidden="0" customHeight="1">
+    <x:row r="104" ht="24" hidden="0" customHeight="1">
       <x:c r="A104" s="19" t="str">
-        <x:v>kt_appliances</x:v>
+        <x:v>kt_freezer</x:v>
       </x:c>
       <x:c r="B104" s="19" t="str">
         <x:v>厨房</x:v>
@@ -4088,13 +4090,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D104" s="19" t="str">
-        <x:v>厨房小电器</x:v>
+        <x:v>是否需要冰柜</x:v>
       </x:c>
       <x:c r="E104" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F104" s="22" t="str">
-        <x:v>空气炸锅 / 微波炉 / 蒸烤箱 / 消毒柜 / 咖啡机 / 燃气热水器 / 垃圾处理器 / 电饭煲</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G104" s="25" t="str">
         <x:v>选填</x:v>
@@ -4106,31 +4108,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J104" s="22" t="str">
-        <x:v>插座数量与台面空间</x:v>
+        <x:v>位置与电源预留</x:v>
       </x:c>
       <x:c r="K104" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L104" s="22" t="str"/>
     </x:row>
-    <x:row r="105" ht="84" hidden="0" customHeight="1">
+    <x:row r="105" ht="120" hidden="0" customHeight="1">
       <x:c r="A105" s="19" t="str">
-        <x:v>kt_storage</x:v>
+        <x:v>kt_appliances</x:v>
       </x:c>
       <x:c r="B105" s="19" t="str">
         <x:v>厨房</x:v>
       </x:c>
       <x:c r="C105" s="19" t="str">
-        <x:v>收纳</x:v>
+        <x:v>设备</x:v>
       </x:c>
       <x:c r="D105" s="19" t="str">
-        <x:v>备餐与调料收纳</x:v>
+        <x:v>厨房小电器</x:v>
       </x:c>
       <x:c r="E105" s="19" t="str">
         <x:v>多选</x:v>
       </x:c>
       <x:c r="F105" s="22" t="str">
-        <x:v>台面调料架 / 柜内拉篮 / 活动小推车 / 蔬菜收纳筐</x:v>
+        <x:v>空气炸锅 / 微波炉 / 蒸烤箱 / 消毒柜 / 咖啡机 / 燃气热水器 / 垃圾处理器 / 电饭煲</x:v>
       </x:c>
       <x:c r="G105" s="25" t="str">
         <x:v>选填</x:v>
@@ -4142,31 +4144,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J105" s="22" t="str">
-        <x:v>橱柜内部设计</x:v>
+        <x:v>插座数量与台面空间</x:v>
       </x:c>
       <x:c r="K105" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L105" s="22" t="str"/>
     </x:row>
-    <x:row r="106" ht="24" hidden="0" customHeight="1">
+    <x:row r="106" ht="84" hidden="0" customHeight="1">
       <x:c r="A106" s="19" t="str">
-        <x:v>kt_light</x:v>
+        <x:v>kt_storage</x:v>
       </x:c>
       <x:c r="B106" s="19" t="str">
         <x:v>厨房</x:v>
       </x:c>
       <x:c r="C106" s="19" t="str">
-        <x:v>照明</x:v>
+        <x:v>收纳</x:v>
       </x:c>
       <x:c r="D106" s="19" t="str">
-        <x:v>吊柜下照明</x:v>
+        <x:v>备餐与调料收纳</x:v>
       </x:c>
       <x:c r="E106" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F106" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>台面调料架 / 柜内拉篮 / 活动小推车 / 蔬菜收纳筐</x:v>
       </x:c>
       <x:c r="G106" s="25" t="str">
         <x:v>选填</x:v>
@@ -4178,124 +4180,124 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J106" s="22" t="str">
-        <x:v>灯带与电源预留</x:v>
+        <x:v>橱柜内部设计</x:v>
       </x:c>
       <x:c r="K106" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L106" s="22" t="str"/>
     </x:row>
-    <x:row r="107" ht="15" hidden="0" customHeight="1">
+    <x:row r="107" ht="24" hidden="0" customHeight="1">
       <x:c r="A107" s="19" t="str">
-        <x:v>kt_other</x:v>
+        <x:v>kt_light</x:v>
       </x:c>
       <x:c r="B107" s="19" t="str">
         <x:v>厨房</x:v>
       </x:c>
       <x:c r="C107" s="19" t="str">
+        <x:v>照明</x:v>
+      </x:c>
+      <x:c r="D107" s="19" t="str">
+        <x:v>吊柜下照明</x:v>
+      </x:c>
+      <x:c r="E107" s="19" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F107" s="22" t="str">
+        <x:v>需要 / 不需要</x:v>
+      </x:c>
+      <x:c r="G107" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H107" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I107" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J107" s="22" t="str">
+        <x:v>灯带与电源预留</x:v>
+      </x:c>
+      <x:c r="K107" s="19" t="str">
+        <x:v>S3</x:v>
+      </x:c>
+      <x:c r="L107" s="22" t="str"/>
+    </x:row>
+    <x:row r="108" ht="15" hidden="0" customHeight="1">
+      <x:c r="A108" s="19" t="str">
+        <x:v>kt_other</x:v>
+      </x:c>
+      <x:c r="B108" s="19" t="str">
+        <x:v>厨房</x:v>
+      </x:c>
+      <x:c r="C108" s="19" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="D107" s="19" t="str">
+      <x:c r="D108" s="19" t="str">
         <x:v>其他补充</x:v>
       </x:c>
-      <x:c r="E107" s="19" t="str">
+      <x:c r="E108" s="19" t="str">
         <x:v>长文本</x:v>
       </x:c>
-      <x:c r="F107" s="22" t="str">
+      <x:c r="F108" s="22" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G107" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H107" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I107" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J107" s="22" t="str">
+      <x:c r="G108" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H108" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I108" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J108" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K107" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L107" s="22" t="str"/>
-    </x:row>
-    <x:row r="108" ht="24" hidden="0" customHeight="1">
-      <x:c r="A108" s="27" t="str">
+      <x:c r="K108" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L108" s="22" t="str"/>
+    </x:row>
+    <x:row r="109" ht="24" hidden="0" customHeight="1">
+      <x:c r="A109" s="27" t="str">
         <x:v>bl_washer</x:v>
       </x:c>
-      <x:c r="B108" s="27" t="str">
+      <x:c r="B109" s="27" t="str">
         <x:v>阳台</x:v>
       </x:c>
-      <x:c r="C108" s="27" t="str">
+      <x:c r="C109" s="27" t="str">
         <x:v>洗烘</x:v>
       </x:c>
-      <x:c r="D108" s="27" t="str">
+      <x:c r="D109" s="27" t="str">
         <x:v>洗衣机</x:v>
       </x:c>
-      <x:c r="E108" s="27" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F108" s="28" t="str">
+      <x:c r="E109" s="27" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F109" s="28" t="str">
         <x:v>是 / 否</x:v>
       </x:c>
-      <x:c r="G108" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H108" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I108" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J108" s="28" t="str">
+      <x:c r="G109" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H109" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I109" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J109" s="28" t="str">
         <x:v>上下水与插座</x:v>
       </x:c>
-      <x:c r="K108" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L108" s="28" t="str"/>
-    </x:row>
-    <x:row r="109" ht="24" hidden="0" customHeight="1">
-      <x:c r="A109" s="19" t="str">
+      <x:c r="K109" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L109" s="28" t="str"/>
+    </x:row>
+    <x:row r="110" ht="24" hidden="0" customHeight="1">
+      <x:c r="A110" s="19" t="str">
         <x:v>bl_washer_top</x:v>
-      </x:c>
-      <x:c r="B109" s="19" t="str">
-        <x:v>阳台</x:v>
-      </x:c>
-      <x:c r="C109" s="19" t="str">
-        <x:v>洗烘</x:v>
-      </x:c>
-      <x:c r="D109" s="19" t="str">
-        <x:v>洗衣机上方空间利用</x:v>
-      </x:c>
-      <x:c r="E109" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F109" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
-      </x:c>
-      <x:c r="G109" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H109" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I109" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J109" s="22" t="str">
-        <x:v>吊柜或台面方案</x:v>
-      </x:c>
-      <x:c r="K109" s="19" t="str">
-        <x:v>S5</x:v>
-      </x:c>
-      <x:c r="L109" s="22" t="str"/>
-    </x:row>
-    <x:row r="110" ht="36" hidden="0" customHeight="1">
-      <x:c r="A110" s="19" t="str">
-        <x:v>bl_dryer</x:v>
       </x:c>
       <x:c r="B110" s="19" t="str">
         <x:v>阳台</x:v>
@@ -4304,13 +4306,13 @@
         <x:v>洗烘</x:v>
       </x:c>
       <x:c r="D110" s="19" t="str">
-        <x:v>烘干机</x:v>
+        <x:v>洗衣机上方空间利用</x:v>
       </x:c>
       <x:c r="E110" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F110" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G110" s="25" t="str">
         <x:v>选填</x:v>
@@ -4322,16 +4324,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J110" s="22" t="str">
-        <x:v>烘干与晾晒方式取舍</x:v>
+        <x:v>吊柜或台面方案</x:v>
       </x:c>
       <x:c r="K110" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L110" s="22" t="str"/>
     </x:row>
-    <x:row r="111" ht="24" hidden="0" customHeight="1">
+    <x:row r="111" ht="36" hidden="0" customHeight="1">
       <x:c r="A111" s="19" t="str">
-        <x:v>bl_mini</x:v>
+        <x:v>bl_dryer</x:v>
       </x:c>
       <x:c r="B111" s="19" t="str">
         <x:v>阳台</x:v>
@@ -4340,7 +4342,7 @@
         <x:v>洗烘</x:v>
       </x:c>
       <x:c r="D111" s="19" t="str">
-        <x:v>小洗衣机或壁挂洗衣机</x:v>
+        <x:v>烘干机</x:v>
       </x:c>
       <x:c r="E111" s="19" t="str">
         <x:v>单选</x:v>
@@ -4358,16 +4360,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J111" s="22" t="str">
-        <x:v>水电点位与承重</x:v>
+        <x:v>烘干与晾晒方式取舍</x:v>
       </x:c>
       <x:c r="K111" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L111" s="22" t="str"/>
     </x:row>
-    <x:row r="112" ht="15" hidden="0" customHeight="1">
+    <x:row r="112" ht="24" hidden="0" customHeight="1">
       <x:c r="A112" s="19" t="str">
-        <x:v>bl_sink</x:v>
+        <x:v>bl_mini</x:v>
       </x:c>
       <x:c r="B112" s="19" t="str">
         <x:v>阳台</x:v>
@@ -4376,7 +4378,7 @@
         <x:v>洗烘</x:v>
       </x:c>
       <x:c r="D112" s="19" t="str">
-        <x:v>水槽区</x:v>
+        <x:v>小洗衣机或壁挂洗衣机</x:v>
       </x:c>
       <x:c r="E112" s="19" t="str">
         <x:v>单选</x:v>
@@ -4394,16 +4396,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J112" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>水电点位与承重</x:v>
       </x:c>
       <x:c r="K112" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L112" s="22" t="str"/>
     </x:row>
-    <x:row r="113" ht="24" hidden="0" customHeight="1">
+    <x:row r="113" ht="15" hidden="0" customHeight="1">
       <x:c r="A113" s="19" t="str">
-        <x:v>bl_mop</x:v>
+        <x:v>bl_sink</x:v>
       </x:c>
       <x:c r="B113" s="19" t="str">
         <x:v>阳台</x:v>
@@ -4412,7 +4414,7 @@
         <x:v>洗烘</x:v>
       </x:c>
       <x:c r="D113" s="19" t="str">
-        <x:v>拖把池</x:v>
+        <x:v>水槽区</x:v>
       </x:c>
       <x:c r="E113" s="19" t="str">
         <x:v>单选</x:v>
@@ -4430,31 +4432,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J113" s="22" t="str">
-        <x:v>给排水预留</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K113" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L113" s="22" t="str"/>
     </x:row>
-    <x:row r="114" ht="72" hidden="0" customHeight="1">
+    <x:row r="114" ht="24" hidden="0" customHeight="1">
       <x:c r="A114" s="19" t="str">
-        <x:v>bl_hanger</x:v>
+        <x:v>bl_mop</x:v>
       </x:c>
       <x:c r="B114" s="19" t="str">
         <x:v>阳台</x:v>
       </x:c>
       <x:c r="C114" s="19" t="str">
-        <x:v>晾晒</x:v>
+        <x:v>洗烘</x:v>
       </x:c>
       <x:c r="D114" s="19" t="str">
-        <x:v>晾晒方式</x:v>
+        <x:v>拖把池</x:v>
       </x:c>
       <x:c r="E114" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F114" s="22" t="str">
-        <x:v>明装晾衣架 / 暗装晾衣架 / 以烘干为主</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G114" s="25" t="str">
         <x:v>选填</x:v>
@@ -4466,31 +4468,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J114" s="22" t="str">
-        <x:v>顶面电路与阳台形式</x:v>
+        <x:v>给排水预留</x:v>
       </x:c>
       <x:c r="K114" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L114" s="22" t="str"/>
     </x:row>
-    <x:row r="115" ht="24" hidden="0" customHeight="1">
+    <x:row r="115" ht="72" hidden="0" customHeight="1">
       <x:c r="A115" s="19" t="str">
-        <x:v>bl_pet</x:v>
+        <x:v>bl_hanger</x:v>
       </x:c>
       <x:c r="B115" s="19" t="str">
         <x:v>阳台</x:v>
       </x:c>
       <x:c r="C115" s="19" t="str">
-        <x:v>功能</x:v>
+        <x:v>晾晒</x:v>
       </x:c>
       <x:c r="D115" s="19" t="str">
-        <x:v>宠物洗澡或猫窝</x:v>
+        <x:v>晾晒方式</x:v>
       </x:c>
       <x:c r="E115" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F115" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>明装晾衣架 / 暗装晾衣架 / 以烘干为主</x:v>
       </x:c>
       <x:c r="G115" s="25" t="str">
         <x:v>选填</x:v>
@@ -4502,16 +4504,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J115" s="22" t="str">
-        <x:v>给排水与位置</x:v>
+        <x:v>顶面电路与阳台形式</x:v>
       </x:c>
       <x:c r="K115" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L115" s="22" t="str"/>
     </x:row>
-    <x:row r="116" ht="72" hidden="0" customHeight="1">
+    <x:row r="116" ht="24" hidden="0" customHeight="1">
       <x:c r="A116" s="19" t="str">
-        <x:v>bl_func</x:v>
+        <x:v>bl_pet</x:v>
       </x:c>
       <x:c r="B116" s="19" t="str">
         <x:v>阳台</x:v>
@@ -4520,13 +4522,13 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D116" s="19" t="str">
-        <x:v>阳台其他功能</x:v>
+        <x:v>宠物洗澡或猫窝</x:v>
       </x:c>
       <x:c r="E116" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F116" s="22" t="str">
-        <x:v>休闲 / 养花 / 咖啡角 / 健身 / 烧烤 / 其他</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G116" s="25" t="str">
         <x:v>选填</x:v>
@@ -4538,16 +4540,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J116" s="22" t="str">
-        <x:v>家具与景观</x:v>
+        <x:v>给排水与位置</x:v>
       </x:c>
       <x:c r="K116" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L116" s="22" t="str"/>
     </x:row>
-    <x:row r="117" ht="24" hidden="0" customHeight="1">
+    <x:row r="117" ht="72" hidden="0" customHeight="1">
       <x:c r="A117" s="19" t="str">
-        <x:v>bl_window</x:v>
+        <x:v>bl_func</x:v>
       </x:c>
       <x:c r="B117" s="19" t="str">
         <x:v>阳台</x:v>
@@ -4556,13 +4558,13 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D117" s="19" t="str">
-        <x:v>是否封窗</x:v>
+        <x:v>阳台其他功能</x:v>
       </x:c>
       <x:c r="E117" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F117" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>休闲 / 养花 / 咖啡角 / 健身 / 烧烤 / 其他</x:v>
       </x:c>
       <x:c r="G117" s="25" t="str">
         <x:v>选填</x:v>
@@ -4574,16 +4576,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J117" s="22" t="str">
-        <x:v>材质与安全</x:v>
+        <x:v>家具与景观</x:v>
       </x:c>
       <x:c r="K117" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L117" s="22" t="str"/>
     </x:row>
-    <x:row r="118" ht="48" hidden="0" customHeight="1">
+    <x:row r="118" ht="24" hidden="0" customHeight="1">
       <x:c r="A118" s="19" t="str">
-        <x:v>bl_robot</x:v>
+        <x:v>bl_window</x:v>
       </x:c>
       <x:c r="B118" s="19" t="str">
         <x:v>阳台</x:v>
@@ -4592,13 +4594,13 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D118" s="19" t="str">
-        <x:v>扫地机器人或洗地机位置</x:v>
+        <x:v>是否封窗</x:v>
       </x:c>
       <x:c r="E118" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F118" s="22" t="str">
-        <x:v>阳台 / 卫生间 / 玄关 / 厨房</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G118" s="25" t="str">
         <x:v>选填</x:v>
@@ -4610,139 +4612,139 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J118" s="22" t="str">
-        <x:v>电源与回充点位</x:v>
+        <x:v>材质与安全</x:v>
       </x:c>
       <x:c r="K118" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L118" s="22" t="str"/>
     </x:row>
-    <x:row r="119" ht="15" hidden="0" customHeight="1">
+    <x:row r="119" ht="48" hidden="0" customHeight="1">
       <x:c r="A119" s="19" t="str">
-        <x:v>bl_other</x:v>
+        <x:v>bl_robot</x:v>
       </x:c>
       <x:c r="B119" s="19" t="str">
         <x:v>阳台</x:v>
       </x:c>
       <x:c r="C119" s="19" t="str">
+        <x:v>功能</x:v>
+      </x:c>
+      <x:c r="D119" s="19" t="str">
+        <x:v>扫地机器人或洗地机位置</x:v>
+      </x:c>
+      <x:c r="E119" s="19" t="str">
+        <x:v>多选</x:v>
+      </x:c>
+      <x:c r="F119" s="22" t="str">
+        <x:v>阳台 / 卫生间 / 玄关 / 厨房</x:v>
+      </x:c>
+      <x:c r="G119" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H119" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I119" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J119" s="22" t="str">
+        <x:v>电源与回充点位</x:v>
+      </x:c>
+      <x:c r="K119" s="19" t="str">
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="L119" s="22" t="str"/>
+    </x:row>
+    <x:row r="120" ht="15" hidden="0" customHeight="1">
+      <x:c r="A120" s="19" t="str">
+        <x:v>bl_other</x:v>
+      </x:c>
+      <x:c r="B120" s="19" t="str">
+        <x:v>阳台</x:v>
+      </x:c>
+      <x:c r="C120" s="19" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="D119" s="19" t="str">
+      <x:c r="D120" s="19" t="str">
         <x:v>其他需求</x:v>
       </x:c>
-      <x:c r="E119" s="19" t="str">
+      <x:c r="E120" s="19" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F119" s="22" t="str">
+      <x:c r="F120" s="22" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G119" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H119" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I119" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J119" s="22" t="str">
+      <x:c r="G120" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H120" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I120" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J120" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K119" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L119" s="22" t="str"/>
-    </x:row>
-    <x:row r="120" ht="36" hidden="0" customHeight="1">
-      <x:c r="A120" s="27" t="str">
+      <x:c r="K120" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L120" s="22" t="str"/>
+    </x:row>
+    <x:row r="121" ht="36" hidden="0" customHeight="1">
+      <x:c r="A121" s="27" t="str">
         <x:v>br_bed</x:v>
       </x:c>
-      <x:c r="B120" s="27" t="str">
+      <x:c r="B121" s="27" t="str">
         <x:v>主卧</x:v>
       </x:c>
-      <x:c r="C120" s="27" t="str">
+      <x:c r="C121" s="27" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="D120" s="27" t="str">
+      <x:c r="D121" s="27" t="str">
         <x:v>床尺寸</x:v>
       </x:c>
-      <x:c r="E120" s="27" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F120" s="28" t="str">
+      <x:c r="E121" s="27" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F121" s="28" t="str">
         <x:v>1.5m / 1.8m / 2.0m</x:v>
       </x:c>
-      <x:c r="G120" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H120" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I120" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J120" s="28" t="str">
+      <x:c r="G121" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H121" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I121" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J121" s="28" t="str">
         <x:v>卧室尺寸匹配</x:v>
       </x:c>
-      <x:c r="K120" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L120" s="28" t="str"/>
-    </x:row>
-    <x:row r="121" ht="24" hidden="0" customHeight="1">
-      <x:c r="A121" s="19" t="str">
-        <x:v>br_side</x:v>
-      </x:c>
-      <x:c r="B121" s="19" t="str">
-        <x:v>主卧</x:v>
-      </x:c>
-      <x:c r="C121" s="19" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D121" s="19" t="str">
-        <x:v>夫妻睡眠位置</x:v>
-      </x:c>
-      <x:c r="E121" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F121" s="22" t="str">
-        <x:v>男左女右 / 男右女左</x:v>
-      </x:c>
-      <x:c r="G121" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H121" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I121" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J121" s="22" t="str">
-        <x:v>床头灯与开关位置</x:v>
-      </x:c>
-      <x:c r="K121" s="19" t="str">
-        <x:v>S3</x:v>
-      </x:c>
-      <x:c r="L121" s="22" t="str"/>
+      <x:c r="K121" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L121" s="28" t="str"/>
     </x:row>
     <x:row r="122" ht="24" hidden="0" customHeight="1">
       <x:c r="A122" s="19" t="str">
-        <x:v>br_light</x:v>
+        <x:v>br_side</x:v>
       </x:c>
       <x:c r="B122" s="19" t="str">
         <x:v>主卧</x:v>
       </x:c>
       <x:c r="C122" s="19" t="str">
-        <x:v>睡眠与灯光</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="D122" s="19" t="str">
-        <x:v>睡眠灯光需求</x:v>
+        <x:v>夫妻睡眠位置</x:v>
       </x:c>
       <x:c r="E122" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F122" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>男左女右 / 男右女左</x:v>
       </x:c>
       <x:c r="G122" s="25" t="str">
         <x:v>选填</x:v>
@@ -4754,16 +4756,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J122" s="22" t="str">
-        <x:v>灯位与开关</x:v>
+        <x:v>床头灯与开关位置</x:v>
       </x:c>
       <x:c r="K122" s="19" t="str">
         <x:v>S3</x:v>
       </x:c>
       <x:c r="L122" s="22" t="str"/>
     </x:row>
-    <x:row r="123" ht="36" hidden="0" customHeight="1">
+    <x:row r="123" ht="24" hidden="0" customHeight="1">
       <x:c r="A123" s="19" t="str">
-        <x:v>br_night</x:v>
+        <x:v>br_light</x:v>
       </x:c>
       <x:c r="B123" s="19" t="str">
         <x:v>主卧</x:v>
@@ -4772,13 +4774,13 @@
         <x:v>睡眠与灯光</x:v>
       </x:c>
       <x:c r="D123" s="19" t="str">
-        <x:v>起夜习惯</x:v>
+        <x:v>睡眠灯光需求</x:v>
       </x:c>
       <x:c r="E123" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F123" s="22" t="str">
-        <x:v>无 / 偶尔喝水 / 频繁起夜</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G123" s="25" t="str">
         <x:v>选填</x:v>
@@ -4790,16 +4792,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J123" s="22" t="str">
-        <x:v>起夜灯与地面照明</x:v>
+        <x:v>灯位与开关</x:v>
       </x:c>
       <x:c r="K123" s="19" t="str">
         <x:v>S3</x:v>
       </x:c>
       <x:c r="L123" s="22" t="str"/>
     </x:row>
-    <x:row r="124" ht="24" hidden="0" customHeight="1">
+    <x:row r="124" ht="36" hidden="0" customHeight="1">
       <x:c r="A124" s="19" t="str">
-        <x:v>br_read</x:v>
+        <x:v>br_night</x:v>
       </x:c>
       <x:c r="B124" s="19" t="str">
         <x:v>主卧</x:v>
@@ -4808,13 +4810,13 @@
         <x:v>睡眠与灯光</x:v>
       </x:c>
       <x:c r="D124" s="19" t="str">
-        <x:v>床上阅读习惯</x:v>
+        <x:v>起夜习惯</x:v>
       </x:c>
       <x:c r="E124" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F124" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>无 / 偶尔喝水 / 频繁起夜</x:v>
       </x:c>
       <x:c r="G124" s="25" t="str">
         <x:v>选填</x:v>
@@ -4826,7 +4828,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J124" s="22" t="str">
-        <x:v>阅读灯与床头插座</x:v>
+        <x:v>起夜灯与地面照明</x:v>
       </x:c>
       <x:c r="K124" s="19" t="str">
         <x:v>S3</x:v>
@@ -4835,7 +4837,7 @@
     </x:row>
     <x:row r="125" ht="24" hidden="0" customHeight="1">
       <x:c r="A125" s="19" t="str">
-        <x:v>br_quiet</x:v>
+        <x:v>br_read</x:v>
       </x:c>
       <x:c r="B125" s="19" t="str">
         <x:v>主卧</x:v>
@@ -4844,13 +4846,13 @@
         <x:v>睡眠与灯光</x:v>
       </x:c>
       <x:c r="D125" s="19" t="str">
-        <x:v>是否需要隔音</x:v>
+        <x:v>床上阅读习惯</x:v>
       </x:c>
       <x:c r="E125" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F125" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G125" s="25" t="str">
         <x:v>选填</x:v>
@@ -4862,16 +4864,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J125" s="22" t="str">
-        <x:v>窗户与墙体隔音</x:v>
+        <x:v>阅读灯与床头插座</x:v>
       </x:c>
       <x:c r="K125" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L125" s="22" t="str"/>
     </x:row>
     <x:row r="126" ht="24" hidden="0" customHeight="1">
       <x:c r="A126" s="19" t="str">
-        <x:v>br_curtain</x:v>
+        <x:v>br_quiet</x:v>
       </x:c>
       <x:c r="B126" s="19" t="str">
         <x:v>主卧</x:v>
@@ -4880,13 +4882,13 @@
         <x:v>睡眠与灯光</x:v>
       </x:c>
       <x:c r="D126" s="19" t="str">
-        <x:v>窗帘需求</x:v>
+        <x:v>是否需要隔音</x:v>
       </x:c>
       <x:c r="E126" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F126" s="22" t="str">
-        <x:v>全遮光 / 自然采光</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G126" s="25" t="str">
         <x:v>选填</x:v>
@@ -4898,7 +4900,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J126" s="22" t="str">
-        <x:v>窗帘形式与材质</x:v>
+        <x:v>窗户与墙体隔音</x:v>
       </x:c>
       <x:c r="K126" s="19" t="str">
         <x:v>S5</x:v>
@@ -4907,22 +4909,22 @@
     </x:row>
     <x:row r="127" ht="24" hidden="0" customHeight="1">
       <x:c r="A127" s="19" t="str">
-        <x:v>br_av</x:v>
+        <x:v>br_curtain</x:v>
       </x:c>
       <x:c r="B127" s="19" t="str">
         <x:v>主卧</x:v>
       </x:c>
       <x:c r="C127" s="19" t="str">
-        <x:v>功能</x:v>
+        <x:v>睡眠与灯光</x:v>
       </x:c>
       <x:c r="D127" s="19" t="str">
-        <x:v>影音设备</x:v>
+        <x:v>窗帘需求</x:v>
       </x:c>
       <x:c r="E127" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F127" s="22" t="str">
-        <x:v>电视 / 投影 / 无</x:v>
+        <x:v>全遮光 / 自然采光</x:v>
       </x:c>
       <x:c r="G127" s="25" t="str">
         <x:v>选填</x:v>
@@ -4934,16 +4936,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J127" s="22" t="str">
-        <x:v>线路与墙面</x:v>
+        <x:v>窗帘形式与材质</x:v>
       </x:c>
       <x:c r="K127" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L127" s="22" t="str"/>
     </x:row>
     <x:row r="128" ht="24" hidden="0" customHeight="1">
       <x:c r="A128" s="19" t="str">
-        <x:v>br_dresser</x:v>
+        <x:v>br_av</x:v>
       </x:c>
       <x:c r="B128" s="19" t="str">
         <x:v>主卧</x:v>
@@ -4952,13 +4954,13 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D128" s="19" t="str">
-        <x:v>化妆台</x:v>
+        <x:v>影音设备</x:v>
       </x:c>
       <x:c r="E128" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F128" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>电视 / 投影 / 无</x:v>
       </x:c>
       <x:c r="G128" s="25" t="str">
         <x:v>选填</x:v>
@@ -4970,7 +4972,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J128" s="22" t="str">
-        <x:v>镜子与灯光</x:v>
+        <x:v>线路与墙面</x:v>
       </x:c>
       <x:c r="K128" s="19" t="str">
         <x:v>原件</x:v>
@@ -4979,7 +4981,7 @@
     </x:row>
     <x:row r="129" ht="24" hidden="0" customHeight="1">
       <x:c r="A129" s="19" t="str">
-        <x:v>br_desk</x:v>
+        <x:v>br_dresser</x:v>
       </x:c>
       <x:c r="B129" s="19" t="str">
         <x:v>主卧</x:v>
@@ -4988,7 +4990,7 @@
         <x:v>功能</x:v>
       </x:c>
       <x:c r="D129" s="19" t="str">
-        <x:v>书桌</x:v>
+        <x:v>化妆台</x:v>
       </x:c>
       <x:c r="E129" s="19" t="str">
         <x:v>单选</x:v>
@@ -5006,31 +5008,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J129" s="22" t="str">
-        <x:v>电源与照明</x:v>
+        <x:v>镜子与灯光</x:v>
       </x:c>
       <x:c r="K129" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L129" s="22" t="str"/>
     </x:row>
-    <x:row r="130" ht="15" hidden="0" customHeight="1">
+    <x:row r="130" ht="24" hidden="0" customHeight="1">
       <x:c r="A130" s="19" t="str">
-        <x:v>br_storage</x:v>
+        <x:v>br_desk</x:v>
       </x:c>
       <x:c r="B130" s="19" t="str">
         <x:v>主卧</x:v>
       </x:c>
       <x:c r="C130" s="19" t="str">
-        <x:v>收纳</x:v>
+        <x:v>功能</x:v>
       </x:c>
       <x:c r="D130" s="19" t="str">
-        <x:v>需强化收纳</x:v>
+        <x:v>书桌</x:v>
       </x:c>
       <x:c r="E130" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F130" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G130" s="25" t="str">
         <x:v>选填</x:v>
@@ -5042,16 +5044,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J130" s="22" t="str">
-        <x:v>柜体分区</x:v>
+        <x:v>电源与照明</x:v>
       </x:c>
       <x:c r="K130" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L130" s="22" t="str"/>
     </x:row>
-    <x:row r="131" ht="60" hidden="0" customHeight="1">
+    <x:row r="131" ht="15" hidden="0" customHeight="1">
       <x:c r="A131" s="19" t="str">
-        <x:v>br_clothes</x:v>
+        <x:v>br_storage</x:v>
       </x:c>
       <x:c r="B131" s="19" t="str">
         <x:v>主卧</x:v>
@@ -5060,13 +5062,13 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D131" s="19" t="str">
-        <x:v>衣物类型</x:v>
+        <x:v>需强化收纳</x:v>
       </x:c>
       <x:c r="E131" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F131" s="22" t="str">
-        <x:v>长衣 / 短衣 / 叠放 / 被褥 / 配饰</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G131" s="25" t="str">
         <x:v>选填</x:v>
@@ -5078,16 +5080,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J131" s="22" t="str">
-        <x:v>衣柜分区比例</x:v>
+        <x:v>柜体分区</x:v>
       </x:c>
       <x:c r="K131" s="19" t="str">
-        <x:v>S1</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L131" s="22" t="str"/>
     </x:row>
-    <x:row r="132" ht="36" hidden="0" customHeight="1">
+    <x:row r="132" ht="60" hidden="0" customHeight="1">
       <x:c r="A132" s="19" t="str">
-        <x:v>br_secondhand</x:v>
+        <x:v>br_clothes</x:v>
       </x:c>
       <x:c r="B132" s="19" t="str">
         <x:v>主卧</x:v>
@@ -5096,13 +5098,13 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D132" s="19" t="str">
-        <x:v>次净衣区</x:v>
+        <x:v>衣物类型</x:v>
       </x:c>
       <x:c r="E132" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F132" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>长衣 / 短衣 / 叠放 / 被褥 / 配饰</x:v>
       </x:c>
       <x:c r="G132" s="25" t="str">
         <x:v>选填</x:v>
@@ -5114,124 +5116,124 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J132" s="22" t="str">
-        <x:v>衣柜侧边掏空与脏衣篓</x:v>
+        <x:v>衣柜分区比例</x:v>
       </x:c>
       <x:c r="K132" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>S1</x:v>
       </x:c>
       <x:c r="L132" s="22" t="str"/>
     </x:row>
-    <x:row r="133" ht="15" hidden="0" customHeight="1">
+    <x:row r="133" ht="36" hidden="0" customHeight="1">
       <x:c r="A133" s="19" t="str">
-        <x:v>br_other</x:v>
+        <x:v>br_secondhand</x:v>
       </x:c>
       <x:c r="B133" s="19" t="str">
         <x:v>主卧</x:v>
       </x:c>
       <x:c r="C133" s="19" t="str">
+        <x:v>收纳</x:v>
+      </x:c>
+      <x:c r="D133" s="19" t="str">
+        <x:v>次净衣区</x:v>
+      </x:c>
+      <x:c r="E133" s="19" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F133" s="22" t="str">
+        <x:v>需要 / 不需要</x:v>
+      </x:c>
+      <x:c r="G133" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H133" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I133" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J133" s="22" t="str">
+        <x:v>衣柜侧边掏空与脏衣篓</x:v>
+      </x:c>
+      <x:c r="K133" s="19" t="str">
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="L133" s="22" t="str"/>
+    </x:row>
+    <x:row r="134" ht="15" hidden="0" customHeight="1">
+      <x:c r="A134" s="19" t="str">
+        <x:v>br_other</x:v>
+      </x:c>
+      <x:c r="B134" s="19" t="str">
+        <x:v>主卧</x:v>
+      </x:c>
+      <x:c r="C134" s="19" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="D133" s="19" t="str">
+      <x:c r="D134" s="19" t="str">
         <x:v>其他需求</x:v>
       </x:c>
-      <x:c r="E133" s="19" t="str">
+      <x:c r="E134" s="19" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F133" s="22" t="str">
+      <x:c r="F134" s="22" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G133" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H133" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I133" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J133" s="22" t="str">
+      <x:c r="G134" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H134" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I134" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J134" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K133" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L133" s="22" t="str"/>
-    </x:row>
-    <x:row r="134" ht="36" hidden="0" customHeight="1">
-      <x:c r="A134" s="27" t="str">
+      <x:c r="K134" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L134" s="22" t="str"/>
+    </x:row>
+    <x:row r="135" ht="36" hidden="0" customHeight="1">
+      <x:c r="A135" s="27" t="str">
         <x:v>ch_gender_age</x:v>
       </x:c>
-      <x:c r="B134" s="27" t="str">
+      <x:c r="B135" s="27" t="str">
         <x:v>其他卧室</x:v>
       </x:c>
-      <x:c r="C134" s="27" t="str">
+      <x:c r="C135" s="27" t="str">
         <x:v>儿童房</x:v>
       </x:c>
-      <x:c r="D134" s="27" t="str">
+      <x:c r="D135" s="27" t="str">
         <x:v>孩子性别与年龄</x:v>
       </x:c>
-      <x:c r="E134" s="27" t="str">
+      <x:c r="E135" s="27" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F134" s="28" t="str">
+      <x:c r="F135" s="28" t="str">
         <x:v>如 女孩/7岁</x:v>
       </x:c>
-      <x:c r="G134" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H134" s="29" t="str">
+      <x:c r="G135" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H135" s="29" t="str">
         <x:v>次卧</x:v>
       </x:c>
-      <x:c r="I134" s="29" t="str">
+      <x:c r="I135" s="29" t="str">
         <x:v>儿童房</x:v>
       </x:c>
-      <x:c r="J134" s="28" t="str">
+      <x:c r="J135" s="28" t="str">
         <x:v>安全防护与收纳策略</x:v>
       </x:c>
-      <x:c r="K134" s="27" t="str">
+      <x:c r="K135" s="27" t="str">
         <x:v>S5</x:v>
       </x:c>
-      <x:c r="L134" s="28" t="str"/>
-    </x:row>
-    <x:row r="135" ht="24" hidden="0" customHeight="1">
-      <x:c r="A135" s="19" t="str">
-        <x:v>ch_activity</x:v>
-      </x:c>
-      <x:c r="B135" s="19" t="str">
-        <x:v>其他卧室</x:v>
-      </x:c>
-      <x:c r="C135" s="19" t="str">
-        <x:v>儿童房</x:v>
-      </x:c>
-      <x:c r="D135" s="19" t="str">
-        <x:v>活动空间或黑板墙</x:v>
-      </x:c>
-      <x:c r="E135" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F135" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
-      </x:c>
-      <x:c r="G135" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H135" s="25" t="str">
-        <x:v>次卧</x:v>
-      </x:c>
-      <x:c r="I135" s="25" t="str">
-        <x:v>儿童房</x:v>
-      </x:c>
-      <x:c r="J135" s="22" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="K135" s="19" t="str">
-        <x:v>S5</x:v>
-      </x:c>
-      <x:c r="L135" s="22" t="str"/>
+      <x:c r="L135" s="28" t="str"/>
     </x:row>
     <x:row r="136" ht="24" hidden="0" customHeight="1">
       <x:c r="A136" s="19" t="str">
-        <x:v>ch_read</x:v>
+        <x:v>ch_activity</x:v>
       </x:c>
       <x:c r="B136" s="19" t="str">
         <x:v>其他卧室</x:v>
@@ -5240,7 +5242,7 @@
         <x:v>儿童房</x:v>
       </x:c>
       <x:c r="D136" s="19" t="str">
-        <x:v>阅读与陪读区</x:v>
+        <x:v>活动空间或黑板墙</x:v>
       </x:c>
       <x:c r="E136" s="19" t="str">
         <x:v>单选</x:v>
@@ -5258,31 +5260,31 @@
         <x:v>儿童房</x:v>
       </x:c>
       <x:c r="J136" s="22" t="str">
-        <x:v>阅读灯与座位</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K136" s="19" t="str">
-        <x:v>S1</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L136" s="22" t="str"/>
     </x:row>
-    <x:row r="137" ht="15" hidden="0" customHeight="1">
+    <x:row r="137" ht="24" hidden="0" customHeight="1">
       <x:c r="A137" s="19" t="str">
-        <x:v>el_twin</x:v>
+        <x:v>ch_read</x:v>
       </x:c>
       <x:c r="B137" s="19" t="str">
         <x:v>其他卧室</x:v>
       </x:c>
       <x:c r="C137" s="19" t="str">
-        <x:v>长辈房</x:v>
+        <x:v>儿童房</x:v>
       </x:c>
       <x:c r="D137" s="19" t="str">
-        <x:v>是否布置两张单人床</x:v>
+        <x:v>阅读与陪读区</x:v>
       </x:c>
       <x:c r="E137" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F137" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G137" s="25" t="str">
         <x:v>选填</x:v>
@@ -5291,19 +5293,19 @@
         <x:v>次卧</x:v>
       </x:c>
       <x:c r="I137" s="25" t="str">
-        <x:v>长辈房</x:v>
+        <x:v>儿童房</x:v>
       </x:c>
       <x:c r="J137" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>阅读灯与座位</x:v>
       </x:c>
       <x:c r="K137" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>S1</x:v>
       </x:c>
       <x:c r="L137" s="22" t="str"/>
     </x:row>
-    <x:row r="138" ht="24" hidden="0" customHeight="1">
+    <x:row r="138" ht="15" hidden="0" customHeight="1">
       <x:c r="A138" s="19" t="str">
-        <x:v>el_safety</x:v>
+        <x:v>el_twin</x:v>
       </x:c>
       <x:c r="B138" s="19" t="str">
         <x:v>其他卧室</x:v>
@@ -5312,13 +5314,13 @@
         <x:v>长辈房</x:v>
       </x:c>
       <x:c r="D138" s="19" t="str">
-        <x:v>紧急按钮或防滑扶手</x:v>
+        <x:v>是否布置两张单人床</x:v>
       </x:c>
       <x:c r="E138" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F138" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G138" s="25" t="str">
         <x:v>选填</x:v>
@@ -5330,7 +5332,7 @@
         <x:v>长辈房</x:v>
       </x:c>
       <x:c r="J138" s="22" t="str">
-        <x:v>适老安全</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K138" s="19" t="str">
         <x:v>S3</x:v>
@@ -5339,7 +5341,7 @@
     </x:row>
     <x:row r="139" ht="24" hidden="0" customHeight="1">
       <x:c r="A139" s="19" t="str">
-        <x:v>el_equip</x:v>
+        <x:v>el_safety</x:v>
       </x:c>
       <x:c r="B139" s="19" t="str">
         <x:v>其他卧室</x:v>
@@ -5348,7 +5350,7 @@
         <x:v>长辈房</x:v>
       </x:c>
       <x:c r="D139" s="19" t="str">
-        <x:v>按摩椅或医疗设备</x:v>
+        <x:v>紧急按钮或防滑扶手</x:v>
       </x:c>
       <x:c r="E139" s="19" t="str">
         <x:v>单选</x:v>
@@ -5366,31 +5368,31 @@
         <x:v>长辈房</x:v>
       </x:c>
       <x:c r="J139" s="22" t="str">
-        <x:v>通道宽度与电源</x:v>
+        <x:v>适老安全</x:v>
       </x:c>
       <x:c r="K139" s="19" t="str">
         <x:v>S3</x:v>
       </x:c>
       <x:c r="L139" s="22" t="str"/>
     </x:row>
-    <x:row r="140" ht="36" hidden="0" customHeight="1">
+    <x:row r="140" ht="24" hidden="0" customHeight="1">
       <x:c r="A140" s="19" t="str">
-        <x:v>gh_freq</x:v>
+        <x:v>el_equip</x:v>
       </x:c>
       <x:c r="B140" s="19" t="str">
         <x:v>其他卧室</x:v>
       </x:c>
       <x:c r="C140" s="19" t="str">
-        <x:v>客房</x:v>
+        <x:v>长辈房</x:v>
       </x:c>
       <x:c r="D140" s="19" t="str">
-        <x:v>客房使用频率</x:v>
+        <x:v>按摩椅或医疗设备</x:v>
       </x:c>
       <x:c r="E140" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F140" s="22" t="str">
-        <x:v>经常 / 偶尔 / 极少</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G140" s="25" t="str">
         <x:v>选填</x:v>
@@ -5399,75 +5401,73 @@
         <x:v>次卧</x:v>
       </x:c>
       <x:c r="I140" s="25" t="str">
-        <x:v>客房</x:v>
+        <x:v>长辈房</x:v>
       </x:c>
       <x:c r="J140" s="22" t="str">
-        <x:v>是否做多功能房</x:v>
+        <x:v>通道宽度与电源</x:v>
       </x:c>
       <x:c r="K140" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L140" s="22" t="str"/>
     </x:row>
-    <x:row r="141" ht="84" hidden="0" customHeight="1">
+    <x:row r="141" ht="36" hidden="0" customHeight="1">
       <x:c r="A141" s="19" t="str">
-        <x:v>room_type</x:v>
+        <x:v>gh_freq</x:v>
       </x:c>
       <x:c r="B141" s="19" t="str">
         <x:v>其他卧室</x:v>
       </x:c>
       <x:c r="C141" s="19" t="str">
-        <x:v>房间定义</x:v>
+        <x:v>客房</x:v>
       </x:c>
       <x:c r="D141" s="19" t="str">
-        <x:v>这个房间主要用来做什么</x:v>
+        <x:v>客房使用频率</x:v>
       </x:c>
       <x:c r="E141" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F141" s="22" t="str">
-        <x:v>儿童房 / 长辈房 / 客房 / 书房 / 电竞房 / 多功能房 / 其他</x:v>
+        <x:v>经常 / 偶尔 / 极少</x:v>
       </x:c>
       <x:c r="G141" s="25" t="str">
-        <x:v>推荐填写</x:v>
+        <x:v>选填</x:v>
       </x:c>
       <x:c r="H141" s="25" t="str">
         <x:v>次卧</x:v>
       </x:c>
       <x:c r="I141" s="25" t="str">
-        <x:v>全部</x:v>
+        <x:v>客房</x:v>
       </x:c>
       <x:c r="J141" s="22" t="str">
-        <x:v>决定该房间渲染哪些字段</x:v>
+        <x:v>是否做多功能房</x:v>
       </x:c>
       <x:c r="K141" s="19" t="str">
-        <x:v>本次重构</x:v>
-      </x:c>
-      <x:c r="L141" s="22" t="str">
-        <x:v>选完类型后只显示相关字段</x:v>
-      </x:c>
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="L141" s="22" t="str"/>
     </x:row>
     <x:row r="142" ht="84" hidden="0" customHeight="1">
       <x:c r="A142" s="19" t="str">
-        <x:v>room_bed</x:v>
+        <x:v>room_type</x:v>
       </x:c>
       <x:c r="B142" s="19" t="str">
         <x:v>其他卧室</x:v>
       </x:c>
       <x:c r="C142" s="19" t="str">
-        <x:v>通用</x:v>
+        <x:v>房间定义</x:v>
       </x:c>
       <x:c r="D142" s="19" t="str">
-        <x:v>床型与尺寸</x:v>
+        <x:v>这个房间主要用来做什么</x:v>
       </x:c>
       <x:c r="E142" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F142" s="22" t="str">
-        <x:v>不需要 / 1.2m / 1.5m / 1.8m / 高低床 / 沙发床 / 榻榻米</x:v>
+        <x:v>儿童房 / 长辈房 / 客房 / 书房 / 电竞房 / 多功能房 / 其他</x:v>
       </x:c>
       <x:c r="G142" s="25" t="str">
-        <x:v>选填</x:v>
+        <x:v>实例必选</x:v>
       </x:c>
       <x:c r="H142" s="25" t="str">
         <x:v>次卧</x:v>
@@ -5476,18 +5476,18 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J142" s="22" t="str">
-        <x:v>房间尺寸匹配</x:v>
+        <x:v>决定该房间渲染哪些字段</x:v>
       </x:c>
       <x:c r="K142" s="19" t="str">
         <x:v>本次重构</x:v>
       </x:c>
       <x:c r="L142" s="22" t="str">
-        <x:v>各类型通用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" ht="48" hidden="0" customHeight="1">
+        <x:v>选完类型后只显示相关字段</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="84" hidden="0" customHeight="1">
       <x:c r="A143" s="19" t="str">
-        <x:v>room_desk</x:v>
+        <x:v>room_bed</x:v>
       </x:c>
       <x:c r="B143" s="19" t="str">
         <x:v>其他卧室</x:v>
@@ -5496,13 +5496,13 @@
         <x:v>通用</x:v>
       </x:c>
       <x:c r="D143" s="19" t="str">
-        <x:v>书桌</x:v>
+        <x:v>床型与尺寸</x:v>
       </x:c>
       <x:c r="E143" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F143" s="22" t="str">
-        <x:v>不需要 / 固定书桌 / 可升降书桌</x:v>
+        <x:v>不需要 / 1.2m / 1.5m / 1.8m / 高低床 / 沙发床 / 榻榻米</x:v>
       </x:c>
       <x:c r="G143" s="25" t="str">
         <x:v>选填</x:v>
@@ -5514,7 +5514,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J143" s="22" t="str">
-        <x:v>学习与办公需求</x:v>
+        <x:v>房间尺寸匹配</x:v>
       </x:c>
       <x:c r="K143" s="19" t="str">
         <x:v>本次重构</x:v>
@@ -5525,7 +5525,7 @@
     </x:row>
     <x:row r="144" ht="48" hidden="0" customHeight="1">
       <x:c r="A144" s="19" t="str">
-        <x:v>room_storage</x:v>
+        <x:v>room_desk</x:v>
       </x:c>
       <x:c r="B144" s="19" t="str">
         <x:v>其他卧室</x:v>
@@ -5534,13 +5534,13 @@
         <x:v>通用</x:v>
       </x:c>
       <x:c r="D144" s="19" t="str">
-        <x:v>收纳需求</x:v>
+        <x:v>书桌</x:v>
       </x:c>
       <x:c r="E144" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F144" s="22" t="str">
-        <x:v>衣柜 / 书柜 / 玩具柜 / 杂物柜</x:v>
+        <x:v>不需要 / 固定书桌 / 可升降书桌</x:v>
       </x:c>
       <x:c r="G144" s="25" t="str">
         <x:v>选填</x:v>
@@ -5552,7 +5552,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J144" s="22" t="str">
-        <x:v>柜体规划</x:v>
+        <x:v>学习与办公需求</x:v>
       </x:c>
       <x:c r="K144" s="19" t="str">
         <x:v>本次重构</x:v>
@@ -5561,24 +5561,24 @@
         <x:v>各类型通用</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="36" hidden="0" customHeight="1">
+    <x:row r="145" ht="48" hidden="0" customHeight="1">
       <x:c r="A145" s="19" t="str">
-        <x:v>room_other</x:v>
+        <x:v>room_storage</x:v>
       </x:c>
       <x:c r="B145" s="19" t="str">
         <x:v>其他卧室</x:v>
       </x:c>
       <x:c r="C145" s="19" t="str">
-        <x:v>其他</x:v>
+        <x:v>通用</x:v>
       </x:c>
       <x:c r="D145" s="19" t="str">
-        <x:v>其他补充</x:v>
+        <x:v>收纳需求</x:v>
       </x:c>
       <x:c r="E145" s="19" t="str">
-        <x:v>长文本</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F145" s="22" t="str">
-        <x:v>文本</x:v>
+        <x:v>衣柜 / 书柜 / 玩具柜 / 杂物柜</x:v>
       </x:c>
       <x:c r="G145" s="25" t="str">
         <x:v>选填</x:v>
@@ -5590,90 +5590,92 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J145" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>柜体规划</x:v>
       </x:c>
       <x:c r="K145" s="19" t="str">
         <x:v>本次重构</x:v>
       </x:c>
       <x:c r="L145" s="22" t="str">
+        <x:v>各类型通用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="36" hidden="0" customHeight="1">
+      <x:c r="A146" s="19" t="str">
+        <x:v>room_other</x:v>
+      </x:c>
+      <x:c r="B146" s="19" t="str">
+        <x:v>其他卧室</x:v>
+      </x:c>
+      <x:c r="C146" s="19" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="D146" s="19" t="str">
+        <x:v>其他补充</x:v>
+      </x:c>
+      <x:c r="E146" s="19" t="str">
+        <x:v>长文本</x:v>
+      </x:c>
+      <x:c r="F146" s="22" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="G146" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H146" s="25" t="str">
+        <x:v>次卧</x:v>
+      </x:c>
+      <x:c r="I146" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J146" s="22" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K146" s="19" t="str">
+        <x:v>本次重构</x:v>
+      </x:c>
+      <x:c r="L146" s="22" t="str">
         <x:v>助手建议会写回这里</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="36" hidden="0" customHeight="1">
-      <x:c r="A146" s="27" t="str">
+    <x:row r="147" ht="36" hidden="0" customHeight="1">
+      <x:c r="A147" s="27" t="str">
         <x:v>st_open</x:v>
       </x:c>
-      <x:c r="B146" s="27" t="str">
+      <x:c r="B147" s="27" t="str">
         <x:v>书房与电竞房</x:v>
       </x:c>
-      <x:c r="C146" s="27" t="str">
+      <x:c r="C147" s="27" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="D146" s="27" t="str">
+      <x:c r="D147" s="27" t="str">
         <x:v>空间开放度</x:v>
       </x:c>
-      <x:c r="E146" s="27" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F146" s="28" t="str">
+      <x:c r="E147" s="27" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F147" s="28" t="str">
         <x:v>完全封闭 / 半开放 / 开放</x:v>
       </x:c>
-      <x:c r="G146" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H146" s="29" t="str">
+      <x:c r="G147" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H147" s="29" t="str">
         <x:v>书房</x:v>
       </x:c>
-      <x:c r="I146" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J146" s="28" t="str">
+      <x:c r="I147" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J147" s="28" t="str">
         <x:v>隔音与展示</x:v>
       </x:c>
-      <x:c r="K146" s="27" t="str">
+      <x:c r="K147" s="27" t="str">
         <x:v>S3</x:v>
       </x:c>
-      <x:c r="L146" s="28" t="str"/>
-    </x:row>
-    <x:row r="147" ht="15" hidden="0" customHeight="1">
-      <x:c r="A147" s="19" t="str">
+      <x:c r="L147" s="28" t="str"/>
+    </x:row>
+    <x:row r="148" ht="15" hidden="0" customHeight="1">
+      <x:c r="A148" s="19" t="str">
         <x:v>st_bedroom</x:v>
-      </x:c>
-      <x:c r="B147" s="19" t="str">
-        <x:v>书房与电竞房</x:v>
-      </x:c>
-      <x:c r="C147" s="19" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D147" s="19" t="str">
-        <x:v>兼具卧室功能</x:v>
-      </x:c>
-      <x:c r="E147" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F147" s="22" t="str">
-        <x:v>是 / 否</x:v>
-      </x:c>
-      <x:c r="G147" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H147" s="25" t="str">
-        <x:v>书房</x:v>
-      </x:c>
-      <x:c r="I147" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J147" s="22" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="K147" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L147" s="22" t="str"/>
-    </x:row>
-    <x:row r="148" ht="24" hidden="0" customHeight="1">
-      <x:c r="A148" s="19" t="str">
-        <x:v>st_cloakroom</x:v>
       </x:c>
       <x:c r="B148" s="19" t="str">
         <x:v>书房与电竞房</x:v>
@@ -5682,7 +5684,7 @@
         <x:v>基础</x:v>
       </x:c>
       <x:c r="D148" s="19" t="str">
-        <x:v>与衣帽间一体化</x:v>
+        <x:v>兼具卧室功能</x:v>
       </x:c>
       <x:c r="E148" s="19" t="str">
         <x:v>单选</x:v>
@@ -5700,31 +5702,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J148" s="22" t="str">
-        <x:v>与收纳分区联动</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K148" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L148" s="22" t="str"/>
     </x:row>
-    <x:row r="149" ht="15" hidden="0" customHeight="1">
+    <x:row r="149" ht="24" hidden="0" customHeight="1">
       <x:c r="A149" s="19" t="str">
-        <x:v>st_books</x:v>
+        <x:v>st_cloakroom</x:v>
       </x:c>
       <x:c r="B149" s="19" t="str">
         <x:v>书房与电竞房</x:v>
       </x:c>
       <x:c r="C149" s="19" t="str">
-        <x:v>收纳</x:v>
+        <x:v>基础</x:v>
       </x:c>
       <x:c r="D149" s="19" t="str">
-        <x:v>藏书量</x:v>
+        <x:v>与衣帽间一体化</x:v>
       </x:c>
       <x:c r="E149" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F149" s="22" t="str">
-        <x:v>多 / 少</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G149" s="25" t="str">
         <x:v>选填</x:v>
@@ -5736,16 +5738,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J149" s="22" t="str">
-        <x:v>书柜容量</x:v>
+        <x:v>与收纳分区联动</x:v>
       </x:c>
       <x:c r="K149" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L149" s="22" t="str"/>
     </x:row>
-    <x:row r="150" ht="24" hidden="0" customHeight="1">
+    <x:row r="150" ht="15" hidden="0" customHeight="1">
       <x:c r="A150" s="19" t="str">
-        <x:v>st_buybooks</x:v>
+        <x:v>st_books</x:v>
       </x:c>
       <x:c r="B150" s="19" t="str">
         <x:v>书房与电竞房</x:v>
@@ -5754,13 +5756,13 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D150" s="19" t="str">
-        <x:v>是否定期买书</x:v>
+        <x:v>藏书量</x:v>
       </x:c>
       <x:c r="E150" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F150" s="22" t="str">
-        <x:v>是 / 否</x:v>
+        <x:v>多 / 少</x:v>
       </x:c>
       <x:c r="G150" s="25" t="str">
         <x:v>选填</x:v>
@@ -5772,7 +5774,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J150" s="22" t="str">
-        <x:v>书柜预留余量</x:v>
+        <x:v>书柜容量</x:v>
       </x:c>
       <x:c r="K150" s="19" t="str">
         <x:v>S3</x:v>
@@ -5781,22 +5783,22 @@
     </x:row>
     <x:row r="151" ht="24" hidden="0" customHeight="1">
       <x:c r="A151" s="19" t="str">
-        <x:v>st_desktop</x:v>
+        <x:v>st_buybooks</x:v>
       </x:c>
       <x:c r="B151" s="19" t="str">
         <x:v>书房与电竞房</x:v>
       </x:c>
       <x:c r="C151" s="19" t="str">
-        <x:v>设备</x:v>
+        <x:v>收纳</x:v>
       </x:c>
       <x:c r="D151" s="19" t="str">
-        <x:v>台式电脑数量</x:v>
+        <x:v>是否定期买书</x:v>
       </x:c>
       <x:c r="E151" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F151" s="22" t="str">
-        <x:v>无 / 1台 / 2台</x:v>
+        <x:v>是 / 否</x:v>
       </x:c>
       <x:c r="G151" s="25" t="str">
         <x:v>选填</x:v>
@@ -5808,7 +5810,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J151" s="22" t="str">
-        <x:v>桌面尺寸与插座</x:v>
+        <x:v>书柜预留余量</x:v>
       </x:c>
       <x:c r="K151" s="19" t="str">
         <x:v>S3</x:v>
@@ -5817,7 +5819,7 @@
     </x:row>
     <x:row r="152" ht="24" hidden="0" customHeight="1">
       <x:c r="A152" s="19" t="str">
-        <x:v>st_laptop</x:v>
+        <x:v>st_desktop</x:v>
       </x:c>
       <x:c r="B152" s="19" t="str">
         <x:v>书房与电竞房</x:v>
@@ -5826,7 +5828,7 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D152" s="19" t="str">
-        <x:v>笔记本电脑数量</x:v>
+        <x:v>台式电脑数量</x:v>
       </x:c>
       <x:c r="E152" s="19" t="str">
         <x:v>单选</x:v>
@@ -5844,7 +5846,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J152" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>桌面尺寸与插座</x:v>
       </x:c>
       <x:c r="K152" s="19" t="str">
         <x:v>S3</x:v>
@@ -5853,7 +5855,7 @@
     </x:row>
     <x:row r="153" ht="24" hidden="0" customHeight="1">
       <x:c r="A153" s="19" t="str">
-        <x:v>st_printer</x:v>
+        <x:v>st_laptop</x:v>
       </x:c>
       <x:c r="B153" s="19" t="str">
         <x:v>书房与电竞房</x:v>
@@ -5862,13 +5864,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D153" s="19" t="str">
-        <x:v>打印机</x:v>
+        <x:v>笔记本电脑数量</x:v>
       </x:c>
       <x:c r="E153" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F153" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>无 / 1台 / 2台</x:v>
       </x:c>
       <x:c r="G153" s="25" t="str">
         <x:v>选填</x:v>
@@ -5880,16 +5882,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J153" s="22" t="str">
-        <x:v>设备区与插座</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K153" s="19" t="str">
         <x:v>S3</x:v>
       </x:c>
       <x:c r="L153" s="22" t="str"/>
     </x:row>
-    <x:row r="154" ht="15" hidden="0" customHeight="1">
+    <x:row r="154" ht="24" hidden="0" customHeight="1">
       <x:c r="A154" s="19" t="str">
-        <x:v>st_device_count</x:v>
+        <x:v>st_printer</x:v>
       </x:c>
       <x:c r="B154" s="19" t="str">
         <x:v>书房与电竞房</x:v>
@@ -5898,13 +5900,13 @@
         <x:v>设备</x:v>
       </x:c>
       <x:c r="D154" s="19" t="str">
-        <x:v>需配置电器数量</x:v>
+        <x:v>打印机</x:v>
       </x:c>
       <x:c r="E154" s="19" t="str">
-        <x:v>数字</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F154" s="22" t="str">
-        <x:v>台</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G154" s="25" t="str">
         <x:v>选填</x:v>
@@ -5916,31 +5918,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J154" s="22" t="str">
-        <x:v>插座数量</x:v>
+        <x:v>设备区与插座</x:v>
       </x:c>
       <x:c r="K154" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L154" s="22" t="str"/>
     </x:row>
-    <x:row r="155" ht="24" hidden="0" customHeight="1">
+    <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="19" t="str">
-        <x:v>st_users</x:v>
+        <x:v>st_device_count</x:v>
       </x:c>
       <x:c r="B155" s="19" t="str">
         <x:v>书房与电竞房</x:v>
       </x:c>
       <x:c r="C155" s="19" t="str">
-        <x:v>使用</x:v>
+        <x:v>设备</x:v>
       </x:c>
       <x:c r="D155" s="19" t="str">
-        <x:v>同时使用人数</x:v>
+        <x:v>需配置电器数量</x:v>
       </x:c>
       <x:c r="E155" s="19" t="str">
         <x:v>数字</x:v>
       </x:c>
       <x:c r="F155" s="22" t="str">
-        <x:v>人</x:v>
+        <x:v>台</x:v>
       </x:c>
       <x:c r="G155" s="25" t="str">
         <x:v>选填</x:v>
@@ -5952,16 +5954,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J155" s="22" t="str">
-        <x:v>桌面与座位数量</x:v>
+        <x:v>插座数量</x:v>
       </x:c>
       <x:c r="K155" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L155" s="22" t="str"/>
     </x:row>
     <x:row r="156" ht="24" hidden="0" customHeight="1">
       <x:c r="A156" s="19" t="str">
-        <x:v>st_live</x:v>
+        <x:v>st_users</x:v>
       </x:c>
       <x:c r="B156" s="19" t="str">
         <x:v>书房与电竞房</x:v>
@@ -5970,13 +5972,13 @@
         <x:v>使用</x:v>
       </x:c>
       <x:c r="D156" s="19" t="str">
-        <x:v>是否需要直播或录音</x:v>
+        <x:v>同时使用人数</x:v>
       </x:c>
       <x:c r="E156" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>数字</x:v>
       </x:c>
       <x:c r="F156" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>人</x:v>
       </x:c>
       <x:c r="G156" s="25" t="str">
         <x:v>选填</x:v>
@@ -5988,16 +5990,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J156" s="22" t="str">
-        <x:v>隔音处理</x:v>
+        <x:v>桌面与座位数量</x:v>
       </x:c>
       <x:c r="K156" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L156" s="22" t="str"/>
     </x:row>
-    <x:row r="157" ht="48" hidden="0" customHeight="1">
+    <x:row r="157" ht="24" hidden="0" customHeight="1">
       <x:c r="A157" s="19" t="str">
-        <x:v>st_network</x:v>
+        <x:v>st_live</x:v>
       </x:c>
       <x:c r="B157" s="19" t="str">
         <x:v>书房与电竞房</x:v>
@@ -6006,13 +6008,13 @@
         <x:v>使用</x:v>
       </x:c>
       <x:c r="D157" s="19" t="str">
-        <x:v>网络与插座需求</x:v>
+        <x:v>是否需要直播或录音</x:v>
       </x:c>
       <x:c r="E157" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F157" s="22" t="str">
-        <x:v>有线上网口 / 多插座 / USB插座</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G157" s="25" t="str">
         <x:v>选填</x:v>
@@ -6024,31 +6026,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J157" s="22" t="str">
-        <x:v>弱电点位</x:v>
+        <x:v>隔音处理</x:v>
       </x:c>
       <x:c r="K157" s="19" t="str">
         <x:v>S4</x:v>
       </x:c>
       <x:c r="L157" s="22" t="str"/>
     </x:row>
-    <x:row r="158" ht="15" hidden="0" customHeight="1">
+    <x:row r="158" ht="48" hidden="0" customHeight="1">
       <x:c r="A158" s="19" t="str">
-        <x:v>st_other</x:v>
+        <x:v>st_network</x:v>
       </x:c>
       <x:c r="B158" s="19" t="str">
         <x:v>书房与电竞房</x:v>
       </x:c>
       <x:c r="C158" s="19" t="str">
-        <x:v>其他</x:v>
+        <x:v>使用</x:v>
       </x:c>
       <x:c r="D158" s="19" t="str">
-        <x:v>其他需求</x:v>
+        <x:v>网络与插座需求</x:v>
       </x:c>
       <x:c r="E158" s="19" t="str">
-        <x:v>文本</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F158" s="22" t="str">
-        <x:v>文本</x:v>
+        <x:v>有线上网口 / 多插座 / USB插座</x:v>
       </x:c>
       <x:c r="G158" s="25" t="str">
         <x:v>选填</x:v>
@@ -6060,88 +6062,88 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J158" s="22" t="str">
+        <x:v>弱电点位</x:v>
+      </x:c>
+      <x:c r="K158" s="19" t="str">
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="L158" s="22" t="str"/>
+    </x:row>
+    <x:row r="159" ht="15" hidden="0" customHeight="1">
+      <x:c r="A159" s="19" t="str">
+        <x:v>st_other</x:v>
+      </x:c>
+      <x:c r="B159" s="19" t="str">
+        <x:v>书房与电竞房</x:v>
+      </x:c>
+      <x:c r="C159" s="19" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="D159" s="19" t="str">
+        <x:v>其他需求</x:v>
+      </x:c>
+      <x:c r="E159" s="19" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="F159" s="22" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="G159" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H159" s="25" t="str">
+        <x:v>书房</x:v>
+      </x:c>
+      <x:c r="I159" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J159" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K158" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L158" s="22" t="str"/>
-    </x:row>
-    <x:row r="159" ht="15" hidden="0" customHeight="1">
-      <x:c r="A159" s="27" t="str">
+      <x:c r="K159" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L159" s="22" t="str"/>
+    </x:row>
+    <x:row r="160" ht="15" hidden="0" customHeight="1">
+      <x:c r="A160" s="27" t="str">
         <x:v>wc_drywet</x:v>
       </x:c>
-      <x:c r="B159" s="27" t="str">
+      <x:c r="B160" s="27" t="str">
         <x:v>卫生间</x:v>
       </x:c>
-      <x:c r="C159" s="27" t="str">
+      <x:c r="C160" s="27" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="D159" s="27" t="str">
+      <x:c r="D160" s="27" t="str">
         <x:v>干湿分离</x:v>
       </x:c>
-      <x:c r="E159" s="27" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F159" s="28" t="str">
+      <x:c r="E160" s="27" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F160" s="28" t="str">
         <x:v>是 / 否</x:v>
       </x:c>
-      <x:c r="G159" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H159" s="29" t="str">
+      <x:c r="G160" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H160" s="29" t="str">
         <x:v>卫生间</x:v>
       </x:c>
-      <x:c r="I159" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J159" s="28" t="str">
+      <x:c r="I160" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J160" s="28" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K159" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L159" s="28" t="str"/>
-    </x:row>
-    <x:row r="160" ht="24" hidden="0" customHeight="1">
-      <x:c r="A160" s="19" t="str">
-        <x:v>wc_hidden</x:v>
-      </x:c>
-      <x:c r="B160" s="19" t="str">
-        <x:v>卫生间</x:v>
-      </x:c>
-      <x:c r="C160" s="19" t="str">
-        <x:v>收纳</x:v>
-      </x:c>
-      <x:c r="D160" s="19" t="str">
-        <x:v>隐形储物间</x:v>
-      </x:c>
-      <x:c r="E160" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F160" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
-      </x:c>
-      <x:c r="G160" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H160" s="25" t="str">
-        <x:v>卫生间</x:v>
-      </x:c>
-      <x:c r="I160" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J160" s="22" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="K160" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L160" s="22" t="str"/>
+      <x:c r="K160" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L160" s="28" t="str"/>
     </x:row>
     <x:row r="161" ht="24" hidden="0" customHeight="1">
       <x:c r="A161" s="19" t="str">
-        <x:v>wc_dresser</x:v>
+        <x:v>wc_hidden</x:v>
       </x:c>
       <x:c r="B161" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6150,7 +6152,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D161" s="19" t="str">
-        <x:v>化妆台</x:v>
+        <x:v>隐形储物间</x:v>
       </x:c>
       <x:c r="E161" s="19" t="str">
         <x:v>单选</x:v>
@@ -6168,16 +6170,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J161" s="22" t="str">
-        <x:v>化妆区灯光与收纳</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K161" s="19" t="str">
-        <x:v>S5</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L161" s="22" t="str"/>
     </x:row>
     <x:row r="162" ht="24" hidden="0" customHeight="1">
       <x:c r="A162" s="19" t="str">
-        <x:v>wc_laundry</x:v>
+        <x:v>wc_dresser</x:v>
       </x:c>
       <x:c r="B162" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6186,7 +6188,7 @@
         <x:v>收纳</x:v>
       </x:c>
       <x:c r="D162" s="19" t="str">
-        <x:v>脏衣区</x:v>
+        <x:v>化妆台</x:v>
       </x:c>
       <x:c r="E162" s="19" t="str">
         <x:v>单选</x:v>
@@ -6204,31 +6206,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J162" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>化妆区灯光与收纳</x:v>
       </x:c>
       <x:c r="K162" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S5</x:v>
       </x:c>
       <x:c r="L162" s="22" t="str"/>
     </x:row>
-    <x:row r="163" ht="36" hidden="0" customHeight="1">
+    <x:row r="163" ht="24" hidden="0" customHeight="1">
       <x:c r="A163" s="19" t="str">
-        <x:v>wc_toilet</x:v>
+        <x:v>wc_laundry</x:v>
       </x:c>
       <x:c r="B163" s="19" t="str">
         <x:v>卫生间</x:v>
       </x:c>
       <x:c r="C163" s="19" t="str">
-        <x:v>洁具</x:v>
+        <x:v>收纳</x:v>
       </x:c>
       <x:c r="D163" s="19" t="str">
-        <x:v>马桶类型</x:v>
+        <x:v>脏衣区</x:v>
       </x:c>
       <x:c r="E163" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F163" s="22" t="str">
-        <x:v>智能马桶 / 普通马桶 / 蹲便</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G163" s="25" t="str">
         <x:v>选填</x:v>
@@ -6240,16 +6242,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
-        <x:v>插座与排污移位</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K163" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L163" s="22" t="str"/>
     </x:row>
-    <x:row r="164" ht="48" hidden="0" customHeight="1">
+    <x:row r="164" ht="36" hidden="0" customHeight="1">
       <x:c r="A164" s="19" t="str">
-        <x:v>wc_bath</x:v>
+        <x:v>wc_toilet</x:v>
       </x:c>
       <x:c r="B164" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6258,16 +6260,16 @@
         <x:v>洁具</x:v>
       </x:c>
       <x:c r="D164" s="19" t="str">
-        <x:v>泡澡需求</x:v>
+        <x:v>马桶类型</x:v>
       </x:c>
       <x:c r="E164" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F164" s="22" t="str">
-        <x:v>浴缸 / 淋浴 / 浴缸加淋浴</x:v>
+        <x:v>智能马桶 / 普通马桶 / 蹲便</x:v>
       </x:c>
       <x:c r="G164" s="25" t="str">
-        <x:v>推荐填写</x:v>
+        <x:v>选填</x:v>
       </x:c>
       <x:c r="H164" s="25" t="str">
         <x:v>卫生间</x:v>
@@ -6276,16 +6278,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J164" s="22" t="str">
-        <x:v>空间与给排水</x:v>
+        <x:v>插座与排污移位</x:v>
       </x:c>
       <x:c r="K164" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L164" s="22" t="str"/>
     </x:row>
-    <x:row r="165" ht="24" hidden="0" customHeight="1">
+    <x:row r="165" ht="48" hidden="0" customHeight="1">
       <x:c r="A165" s="19" t="str">
-        <x:v>wc_shower</x:v>
+        <x:v>wc_bath</x:v>
       </x:c>
       <x:c r="B165" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6294,16 +6296,16 @@
         <x:v>洁具</x:v>
       </x:c>
       <x:c r="D165" s="19" t="str">
-        <x:v>淋浴形式</x:v>
+        <x:v>泡澡需求</x:v>
       </x:c>
       <x:c r="E165" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F165" s="22" t="str">
-        <x:v>淋浴房玻璃 / 浴帘</x:v>
+        <x:v>浴缸 / 淋浴 / 浴缸加淋浴</x:v>
       </x:c>
       <x:c r="G165" s="25" t="str">
-        <x:v>选填</x:v>
+        <x:v>推荐填写</x:v>
       </x:c>
       <x:c r="H165" s="25" t="str">
         <x:v>卫生间</x:v>
@@ -6312,16 +6314,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J165" s="22" t="str">
-        <x:v>清洁与空间</x:v>
+        <x:v>空间与给排水</x:v>
       </x:c>
       <x:c r="K165" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L165" s="22" t="str"/>
     </x:row>
     <x:row r="166" ht="24" hidden="0" customHeight="1">
       <x:c r="A166" s="19" t="str">
-        <x:v>wc_sink</x:v>
+        <x:v>wc_shower</x:v>
       </x:c>
       <x:c r="B166" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6330,13 +6332,13 @@
         <x:v>洁具</x:v>
       </x:c>
       <x:c r="D166" s="19" t="str">
-        <x:v>洗手盆</x:v>
+        <x:v>淋浴形式</x:v>
       </x:c>
       <x:c r="E166" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F166" s="22" t="str">
-        <x:v>单盆 / 双盆</x:v>
+        <x:v>淋浴房玻璃 / 浴帘</x:v>
       </x:c>
       <x:c r="G166" s="25" t="str">
         <x:v>选填</x:v>
@@ -6348,7 +6350,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J166" s="22" t="str">
-        <x:v>台面尺寸</x:v>
+        <x:v>清洁与空间</x:v>
       </x:c>
       <x:c r="K166" s="19" t="str">
         <x:v>S3</x:v>
@@ -6357,7 +6359,7 @@
     </x:row>
     <x:row r="167" ht="24" hidden="0" customHeight="1">
       <x:c r="A167" s="19" t="str">
-        <x:v>wc_safe</x:v>
+        <x:v>wc_sink</x:v>
       </x:c>
       <x:c r="B167" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6366,13 +6368,13 @@
         <x:v>洁具</x:v>
       </x:c>
       <x:c r="D167" s="19" t="str">
-        <x:v>紧急按钮或防滑扶手</x:v>
+        <x:v>洗手盆</x:v>
       </x:c>
       <x:c r="E167" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F167" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>单盆 / 双盆</x:v>
       </x:c>
       <x:c r="G167" s="25" t="str">
         <x:v>选填</x:v>
@@ -6384,7 +6386,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J167" s="22" t="str">
-        <x:v>适老安全</x:v>
+        <x:v>台面尺寸</x:v>
       </x:c>
       <x:c r="K167" s="19" t="str">
         <x:v>S3</x:v>
@@ -6393,7 +6395,7 @@
     </x:row>
     <x:row r="168" ht="24" hidden="0" customHeight="1">
       <x:c r="A168" s="19" t="str">
-        <x:v>wc_spray</x:v>
+        <x:v>wc_safe</x:v>
       </x:c>
       <x:c r="B168" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6402,7 +6404,7 @@
         <x:v>洁具</x:v>
       </x:c>
       <x:c r="D168" s="19" t="str">
-        <x:v>喷枪</x:v>
+        <x:v>紧急按钮或防滑扶手</x:v>
       </x:c>
       <x:c r="E168" s="19" t="str">
         <x:v>单选</x:v>
@@ -6420,7 +6422,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J168" s="22" t="str">
-        <x:v>给水点位</x:v>
+        <x:v>适老安全</x:v>
       </x:c>
       <x:c r="K168" s="19" t="str">
         <x:v>S3</x:v>
@@ -6429,16 +6431,16 @@
     </x:row>
     <x:row r="169" ht="24" hidden="0" customHeight="1">
       <x:c r="A169" s="19" t="str">
-        <x:v>wc_towel</x:v>
+        <x:v>wc_spray</x:v>
       </x:c>
       <x:c r="B169" s="19" t="str">
         <x:v>卫生间</x:v>
       </x:c>
       <x:c r="C169" s="19" t="str">
-        <x:v>电器</x:v>
+        <x:v>洁具</x:v>
       </x:c>
       <x:c r="D169" s="19" t="str">
-        <x:v>电热毛巾架</x:v>
+        <x:v>喷枪</x:v>
       </x:c>
       <x:c r="E169" s="19" t="str">
         <x:v>单选</x:v>
@@ -6456,16 +6458,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J169" s="22" t="str">
-        <x:v>插座预留</x:v>
+        <x:v>给水点位</x:v>
       </x:c>
       <x:c r="K169" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L169" s="22" t="str"/>
     </x:row>
     <x:row r="170" ht="24" hidden="0" customHeight="1">
       <x:c r="A170" s="19" t="str">
-        <x:v>wc_showerhead</x:v>
+        <x:v>wc_towel</x:v>
       </x:c>
       <x:c r="B170" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6474,7 +6476,7 @@
         <x:v>电器</x:v>
       </x:c>
       <x:c r="D170" s="19" t="str">
-        <x:v>恒温花洒</x:v>
+        <x:v>电热毛巾架</x:v>
       </x:c>
       <x:c r="E170" s="19" t="str">
         <x:v>单选</x:v>
@@ -6492,7 +6494,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J170" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>插座预留</x:v>
       </x:c>
       <x:c r="K170" s="19" t="str">
         <x:v>原件</x:v>
@@ -6501,7 +6503,7 @@
     </x:row>
     <x:row r="171" ht="24" hidden="0" customHeight="1">
       <x:c r="A171" s="19" t="str">
-        <x:v>wc_heater</x:v>
+        <x:v>wc_showerhead</x:v>
       </x:c>
       <x:c r="B171" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6510,7 +6512,7 @@
         <x:v>电器</x:v>
       </x:c>
       <x:c r="D171" s="19" t="str">
-        <x:v>暖风机</x:v>
+        <x:v>恒温花洒</x:v>
       </x:c>
       <x:c r="E171" s="19" t="str">
         <x:v>单选</x:v>
@@ -6528,7 +6530,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J171" s="22" t="str">
-        <x:v>顶面电路</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K171" s="19" t="str">
         <x:v>原件</x:v>
@@ -6537,7 +6539,7 @@
     </x:row>
     <x:row r="172" ht="24" hidden="0" customHeight="1">
       <x:c r="A172" s="19" t="str">
-        <x:v>wc_hairdryer</x:v>
+        <x:v>wc_heater</x:v>
       </x:c>
       <x:c r="B172" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6546,7 +6548,7 @@
         <x:v>电器</x:v>
       </x:c>
       <x:c r="D172" s="19" t="str">
-        <x:v>吹风机</x:v>
+        <x:v>暖风机</x:v>
       </x:c>
       <x:c r="E172" s="19" t="str">
         <x:v>单选</x:v>
@@ -6564,7 +6566,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J172" s="22" t="str">
-        <x:v>插座位置</x:v>
+        <x:v>顶面电路</x:v>
       </x:c>
       <x:c r="K172" s="19" t="str">
         <x:v>原件</x:v>
@@ -6573,7 +6575,7 @@
     </x:row>
     <x:row r="173" ht="24" hidden="0" customHeight="1">
       <x:c r="A173" s="19" t="str">
-        <x:v>wc_floorheat</x:v>
+        <x:v>wc_hairdryer</x:v>
       </x:c>
       <x:c r="B173" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6582,7 +6584,7 @@
         <x:v>电器</x:v>
       </x:c>
       <x:c r="D173" s="19" t="str">
-        <x:v>加热地板</x:v>
+        <x:v>吹风机</x:v>
       </x:c>
       <x:c r="E173" s="19" t="str">
         <x:v>单选</x:v>
@@ -6600,25 +6602,25 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J173" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>插座位置</x:v>
       </x:c>
       <x:c r="K173" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L173" s="22" t="str"/>
     </x:row>
     <x:row r="174" ht="24" hidden="0" customHeight="1">
       <x:c r="A174" s="19" t="str">
-        <x:v>wc_mirror</x:v>
+        <x:v>wc_floorheat</x:v>
       </x:c>
       <x:c r="B174" s="19" t="str">
         <x:v>卫生间</x:v>
       </x:c>
       <x:c r="C174" s="19" t="str">
-        <x:v>柜体</x:v>
+        <x:v>电器</x:v>
       </x:c>
       <x:c r="D174" s="19" t="str">
-        <x:v>智能镜柜</x:v>
+        <x:v>加热地板</x:v>
       </x:c>
       <x:c r="E174" s="19" t="str">
         <x:v>单选</x:v>
@@ -6636,16 +6638,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J174" s="22" t="str">
-        <x:v>电源与收纳</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K174" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S3</x:v>
       </x:c>
       <x:c r="L174" s="22" t="str"/>
     </x:row>
     <x:row r="175" ht="24" hidden="0" customHeight="1">
       <x:c r="A175" s="19" t="str">
-        <x:v>wc_mirror_cab</x:v>
+        <x:v>wc_mirror</x:v>
       </x:c>
       <x:c r="B175" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6654,7 +6656,7 @@
         <x:v>柜体</x:v>
       </x:c>
       <x:c r="D175" s="19" t="str">
-        <x:v>收纳镜柜</x:v>
+        <x:v>智能镜柜</x:v>
       </x:c>
       <x:c r="E175" s="19" t="str">
         <x:v>单选</x:v>
@@ -6672,7 +6674,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J175" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>电源与收纳</x:v>
       </x:c>
       <x:c r="K175" s="19" t="str">
         <x:v>原件</x:v>
@@ -6681,7 +6683,7 @@
     </x:row>
     <x:row r="176" ht="24" hidden="0" customHeight="1">
       <x:c r="A176" s="19" t="str">
-        <x:v>wc_basin</x:v>
+        <x:v>wc_mirror_cab</x:v>
       </x:c>
       <x:c r="B176" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6690,7 +6692,7 @@
         <x:v>柜体</x:v>
       </x:c>
       <x:c r="D176" s="19" t="str">
-        <x:v>一体台下盆</x:v>
+        <x:v>收纳镜柜</x:v>
       </x:c>
       <x:c r="E176" s="19" t="str">
         <x:v>单选</x:v>
@@ -6708,7 +6710,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J176" s="22" t="str">
-        <x:v>台面清洁便利性</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K176" s="19" t="str">
         <x:v>原件</x:v>
@@ -6717,7 +6719,7 @@
     </x:row>
     <x:row r="177" ht="24" hidden="0" customHeight="1">
       <x:c r="A177" s="19" t="str">
-        <x:v>wc_outside_cab</x:v>
+        <x:v>wc_basin</x:v>
       </x:c>
       <x:c r="B177" s="19" t="str">
         <x:v>卫生间</x:v>
@@ -6726,7 +6728,7 @@
         <x:v>柜体</x:v>
       </x:c>
       <x:c r="D177" s="19" t="str">
-        <x:v>浴室柜外置</x:v>
+        <x:v>一体台下盆</x:v>
       </x:c>
       <x:c r="E177" s="19" t="str">
         <x:v>单选</x:v>
@@ -6744,31 +6746,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J177" s="22" t="str">
-        <x:v>干湿分区与空间</x:v>
+        <x:v>台面清洁便利性</x:v>
       </x:c>
       <x:c r="K177" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L177" s="22" t="str"/>
     </x:row>
-    <x:row r="178" ht="15" hidden="0" customHeight="1">
+    <x:row r="178" ht="24" hidden="0" customHeight="1">
       <x:c r="A178" s="19" t="str">
-        <x:v>wc_other</x:v>
+        <x:v>wc_outside_cab</x:v>
       </x:c>
       <x:c r="B178" s="19" t="str">
         <x:v>卫生间</x:v>
       </x:c>
       <x:c r="C178" s="19" t="str">
-        <x:v>其他</x:v>
+        <x:v>柜体</x:v>
       </x:c>
       <x:c r="D178" s="19" t="str">
-        <x:v>其他需求</x:v>
+        <x:v>浴室柜外置</x:v>
       </x:c>
       <x:c r="E178" s="19" t="str">
-        <x:v>文本</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F178" s="22" t="str">
-        <x:v>文本</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G178" s="25" t="str">
         <x:v>选填</x:v>
@@ -6780,34 +6782,34 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J178" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>干湿分区与空间</x:v>
       </x:c>
       <x:c r="K178" s="19" t="str">
         <x:v>原件</x:v>
       </x:c>
       <x:c r="L178" s="22" t="str"/>
     </x:row>
-    <x:row r="179" ht="48" hidden="0" customHeight="1">
+    <x:row r="179" ht="15" hidden="0" customHeight="1">
       <x:c r="A179" s="19" t="str">
-        <x:v>wc_type</x:v>
+        <x:v>wc_other</x:v>
       </x:c>
       <x:c r="B179" s="19" t="str">
         <x:v>卫生间</x:v>
       </x:c>
       <x:c r="C179" s="19" t="str">
-        <x:v>房间定义</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="D179" s="19" t="str">
-        <x:v>这间卫生间</x:v>
+        <x:v>其他需求</x:v>
       </x:c>
       <x:c r="E179" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="F179" s="22" t="str">
-        <x:v>主卫 / 客卫 / 次卫 / 其他</x:v>
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="G179" s="25" t="str">
-        <x:v>推荐填写</x:v>
+        <x:v>选填</x:v>
       </x:c>
       <x:c r="H179" s="25" t="str">
         <x:v>卫生间</x:v>
@@ -6816,90 +6818,90 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K179" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L179" s="22" t="str"/>
+    </x:row>
+    <x:row r="180" ht="48" hidden="0" customHeight="1">
+      <x:c r="A180" s="19" t="str">
+        <x:v>wc_type</x:v>
+      </x:c>
+      <x:c r="B180" s="19" t="str">
+        <x:v>卫生间</x:v>
+      </x:c>
+      <x:c r="C180" s="19" t="str">
+        <x:v>房间定义</x:v>
+      </x:c>
+      <x:c r="D180" s="19" t="str">
+        <x:v>这间卫生间</x:v>
+      </x:c>
+      <x:c r="E180" s="19" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F180" s="22" t="str">
+        <x:v>主卫 / 客卫 / 次卫 / 其他</x:v>
+      </x:c>
+      <x:c r="G180" s="25" t="str">
+        <x:v>实例必选</x:v>
+      </x:c>
+      <x:c r="H180" s="25" t="str">
+        <x:v>卫生间</x:v>
+      </x:c>
+      <x:c r="I180" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J180" s="22" t="str">
         <x:v>决定显示名称与差异化建议</x:v>
       </x:c>
-      <x:c r="K179" s="19" t="str">
+      <x:c r="K180" s="19" t="str">
         <x:v>本次重构</x:v>
       </x:c>
-      <x:c r="L179" s="22" t="str">
+      <x:c r="L180" s="22" t="str">
         <x:v>默认主卫、客卫两间</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="15" hidden="0" customHeight="1">
-      <x:c r="A180" s="27" t="str">
+    <x:row r="181" ht="15" hidden="0" customHeight="1">
+      <x:c r="A181" s="27" t="str">
         <x:v>sc_cloakroom</x:v>
       </x:c>
-      <x:c r="B180" s="27" t="str">
+      <x:c r="B181" s="27" t="str">
         <x:v>收纳与家政</x:v>
       </x:c>
-      <x:c r="C180" s="27" t="str">
+      <x:c r="C181" s="27" t="str">
         <x:v>衣帽间</x:v>
       </x:c>
-      <x:c r="D180" s="27" t="str">
+      <x:c r="D181" s="27" t="str">
         <x:v>是否需要衣帽间</x:v>
       </x:c>
-      <x:c r="E180" s="27" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F180" s="28" t="str">
+      <x:c r="E181" s="27" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F181" s="28" t="str">
         <x:v>是 / 否</x:v>
       </x:c>
-      <x:c r="G180" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H180" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I180" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J180" s="28" t="str">
+      <x:c r="G181" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H181" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I181" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J181" s="28" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K180" s="27" t="str">
+      <x:c r="K181" s="27" t="str">
         <x:v>S1</x:v>
       </x:c>
-      <x:c r="L180" s="28" t="str"/>
-    </x:row>
-    <x:row r="181" ht="24" hidden="0" customHeight="1">
-      <x:c r="A181" s="19" t="str">
-        <x:v>sc_cloakroom_share</x:v>
-      </x:c>
-      <x:c r="B181" s="19" t="str">
-        <x:v>收纳与家政</x:v>
-      </x:c>
-      <x:c r="C181" s="19" t="str">
-        <x:v>衣帽间</x:v>
-      </x:c>
-      <x:c r="D181" s="19" t="str">
-        <x:v>衣帽间共用方式</x:v>
-      </x:c>
-      <x:c r="E181" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F181" s="22" t="str">
-        <x:v>共用 / 分开</x:v>
-      </x:c>
-      <x:c r="G181" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H181" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I181" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J181" s="22" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="K181" s="19" t="str">
-        <x:v>S1</x:v>
-      </x:c>
-      <x:c r="L181" s="22" t="str"/>
+      <x:c r="L181" s="28" t="str"/>
     </x:row>
     <x:row r="182" ht="24" hidden="0" customHeight="1">
       <x:c r="A182" s="19" t="str">
-        <x:v>sc_cloakroom_form</x:v>
+        <x:v>sc_cloakroom_share</x:v>
       </x:c>
       <x:c r="B182" s="19" t="str">
         <x:v>收纳与家政</x:v>
@@ -6908,13 +6910,13 @@
         <x:v>衣帽间</x:v>
       </x:c>
       <x:c r="D182" s="19" t="str">
-        <x:v>衣帽间形式</x:v>
+        <x:v>衣帽间共用方式</x:v>
       </x:c>
       <x:c r="E182" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F182" s="22" t="str">
-        <x:v>开放式 / 封闭式</x:v>
+        <x:v>共用 / 分开</x:v>
       </x:c>
       <x:c r="G182" s="25" t="str">
         <x:v>选填</x:v>
@@ -6929,28 +6931,28 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K182" s="19" t="str">
-        <x:v>原件</x:v>
+        <x:v>S1</x:v>
       </x:c>
       <x:c r="L182" s="22" t="str"/>
     </x:row>
-    <x:row r="183" ht="60" hidden="0" customHeight="1">
+    <x:row r="183" ht="24" hidden="0" customHeight="1">
       <x:c r="A183" s="19" t="str">
-        <x:v>sc_storage_room</x:v>
+        <x:v>sc_cloakroom_form</x:v>
       </x:c>
       <x:c r="B183" s="19" t="str">
         <x:v>收纳与家政</x:v>
       </x:c>
       <x:c r="C183" s="19" t="str">
-        <x:v>储物间</x:v>
+        <x:v>衣帽间</x:v>
       </x:c>
       <x:c r="D183" s="19" t="str">
-        <x:v>是否需要储物间</x:v>
+        <x:v>衣帽间形式</x:v>
       </x:c>
       <x:c r="E183" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F183" s="22" t="str">
-        <x:v>独立储物间 / 与其他空间融合 / 不需要</x:v>
+        <x:v>开放式 / 封闭式</x:v>
       </x:c>
       <x:c r="G183" s="25" t="str">
         <x:v>选填</x:v>
@@ -6965,13 +6967,13 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K183" s="19" t="str">
-        <x:v>S1</x:v>
+        <x:v>原件</x:v>
       </x:c>
       <x:c r="L183" s="22" t="str"/>
     </x:row>
-    <x:row r="184" ht="96" hidden="0" customHeight="1">
+    <x:row r="184" ht="60" hidden="0" customHeight="1">
       <x:c r="A184" s="19" t="str">
-        <x:v>sc_storage_items</x:v>
+        <x:v>sc_storage_room</x:v>
       </x:c>
       <x:c r="B184" s="19" t="str">
         <x:v>收纳与家政</x:v>
@@ -6980,13 +6982,13 @@
         <x:v>储物间</x:v>
       </x:c>
       <x:c r="D184" s="19" t="str">
-        <x:v>储物间需要存放的物品</x:v>
+        <x:v>是否需要储物间</x:v>
       </x:c>
       <x:c r="E184" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F184" s="22" t="str">
-        <x:v>吸尘器 / 梯子 / 维修工具 / 行李箱 / 露营装备 / 风扇 / 电暖器 / 换季被褥</x:v>
+        <x:v>独立储物间 / 与其他空间融合 / 不需要</x:v>
       </x:c>
       <x:c r="G184" s="25" t="str">
         <x:v>选填</x:v>
@@ -6998,16 +7000,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J184" s="22" t="str">
-        <x:v>柜体尺寸与分区</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K184" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>S1</x:v>
       </x:c>
       <x:c r="L184" s="22" t="str"/>
     </x:row>
-    <x:row r="185" ht="24" hidden="0" customHeight="1">
+    <x:row r="185" ht="96" hidden="0" customHeight="1">
       <x:c r="A185" s="19" t="str">
-        <x:v>sc_luggage</x:v>
+        <x:v>sc_storage_items</x:v>
       </x:c>
       <x:c r="B185" s="19" t="str">
         <x:v>收纳与家政</x:v>
@@ -7016,13 +7018,13 @@
         <x:v>储物间</x:v>
       </x:c>
       <x:c r="D185" s="19" t="str">
-        <x:v>行李箱数量</x:v>
+        <x:v>储物间需要存放的物品</x:v>
       </x:c>
       <x:c r="E185" s="19" t="str">
-        <x:v>数字</x:v>
+        <x:v>多选</x:v>
       </x:c>
       <x:c r="F185" s="22" t="str">
-        <x:v>个</x:v>
+        <x:v>吸尘器 / 梯子 / 维修工具 / 行李箱 / 露营装备 / 风扇 / 电暖器 / 换季被褥</x:v>
       </x:c>
       <x:c r="G185" s="25" t="str">
         <x:v>选填</x:v>
@@ -7034,7 +7036,7 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J185" s="22" t="str">
-        <x:v>顶柜或底柜预留</x:v>
+        <x:v>柜体尺寸与分区</x:v>
       </x:c>
       <x:c r="K185" s="19" t="str">
         <x:v>S4</x:v>
@@ -7043,22 +7045,22 @@
     </x:row>
     <x:row r="186" ht="24" hidden="0" customHeight="1">
       <x:c r="A186" s="19" t="str">
-        <x:v>sc_collection</x:v>
+        <x:v>sc_luggage</x:v>
       </x:c>
       <x:c r="B186" s="19" t="str">
         <x:v>收纳与家政</x:v>
       </x:c>
       <x:c r="C186" s="19" t="str">
-        <x:v>展示</x:v>
+        <x:v>储物间</x:v>
       </x:c>
       <x:c r="D186" s="19" t="str">
-        <x:v>收藏品展示需求</x:v>
+        <x:v>行李箱数量</x:v>
       </x:c>
       <x:c r="E186" s="19" t="str">
-        <x:v>单选</x:v>
+        <x:v>数字</x:v>
       </x:c>
       <x:c r="F186" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>个</x:v>
       </x:c>
       <x:c r="G186" s="25" t="str">
         <x:v>选填</x:v>
@@ -7070,16 +7072,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J186" s="22" t="str">
-        <x:v>展示柜与藏露比例</x:v>
+        <x:v>顶柜或底柜预留</x:v>
       </x:c>
       <x:c r="K186" s="19" t="str">
         <x:v>S4</x:v>
       </x:c>
       <x:c r="L186" s="22" t="str"/>
     </x:row>
-    <x:row r="187" ht="36" hidden="0" customHeight="1">
+    <x:row r="187" ht="24" hidden="0" customHeight="1">
       <x:c r="A187" s="19" t="str">
-        <x:v>sc_valuable</x:v>
+        <x:v>sc_collection</x:v>
       </x:c>
       <x:c r="B187" s="19" t="str">
         <x:v>收纳与家政</x:v>
@@ -7088,13 +7090,13 @@
         <x:v>展示</x:v>
       </x:c>
       <x:c r="D187" s="19" t="str">
-        <x:v>贵重物品存放</x:v>
+        <x:v>收藏品展示需求</x:v>
       </x:c>
       <x:c r="E187" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F187" s="22" t="str">
-        <x:v>保险箱 / 密码抽 / 无</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G187" s="25" t="str">
         <x:v>选填</x:v>
@@ -7106,31 +7108,31 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J187" s="22" t="str">
-        <x:v>-</x:v>
+        <x:v>展示柜与藏露比例</x:v>
       </x:c>
       <x:c r="K187" s="19" t="str">
-        <x:v>S1</x:v>
+        <x:v>S4</x:v>
       </x:c>
       <x:c r="L187" s="22" t="str"/>
     </x:row>
-    <x:row r="188" ht="24" hidden="0" customHeight="1">
+    <x:row r="188" ht="36" hidden="0" customHeight="1">
       <x:c r="A188" s="19" t="str">
-        <x:v>sc_housekeeping</x:v>
+        <x:v>sc_valuable</x:v>
       </x:c>
       <x:c r="B188" s="19" t="str">
         <x:v>收纳与家政</x:v>
       </x:c>
       <x:c r="C188" s="19" t="str">
-        <x:v>家政</x:v>
+        <x:v>展示</x:v>
       </x:c>
       <x:c r="D188" s="19" t="str">
-        <x:v>家政柜</x:v>
+        <x:v>贵重物品存放</x:v>
       </x:c>
       <x:c r="E188" s="19" t="str">
         <x:v>单选</x:v>
       </x:c>
       <x:c r="F188" s="22" t="str">
-        <x:v>需要 / 不需要</x:v>
+        <x:v>保险箱 / 密码抽 / 无</x:v>
       </x:c>
       <x:c r="G188" s="25" t="str">
         <x:v>选填</x:v>
@@ -7142,16 +7144,16 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J188" s="22" t="str">
-        <x:v>清洁工具集中收纳</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K188" s="19" t="str">
-        <x:v>S4</x:v>
+        <x:v>S1</x:v>
       </x:c>
       <x:c r="L188" s="22" t="str"/>
     </x:row>
-    <x:row r="189" ht="48" hidden="0" customHeight="1">
+    <x:row r="189" ht="24" hidden="0" customHeight="1">
       <x:c r="A189" s="19" t="str">
-        <x:v>sc_seasonal</x:v>
+        <x:v>sc_housekeeping</x:v>
       </x:c>
       <x:c r="B189" s="19" t="str">
         <x:v>收纳与家政</x:v>
@@ -7160,13 +7162,13 @@
         <x:v>家政</x:v>
       </x:c>
       <x:c r="D189" s="19" t="str">
-        <x:v>换季物品存放</x:v>
+        <x:v>家政柜</x:v>
       </x:c>
       <x:c r="E189" s="19" t="str">
-        <x:v>多选</x:v>
+        <x:v>单选</x:v>
       </x:c>
       <x:c r="F189" s="22" t="str">
-        <x:v>被褥 / 羽绒服 / 电风扇 / 取暖器</x:v>
+        <x:v>需要 / 不需要</x:v>
       </x:c>
       <x:c r="G189" s="25" t="str">
         <x:v>选填</x:v>
@@ -7178,126 +7180,126 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="J189" s="22" t="str">
-        <x:v>顶柜预留</x:v>
+        <x:v>清洁工具集中收纳</x:v>
       </x:c>
       <x:c r="K189" s="19" t="str">
-        <x:v>S3</x:v>
+        <x:v>S4</x:v>
       </x:c>
       <x:c r="L189" s="22" t="str"/>
     </x:row>
-    <x:row r="190" ht="36" hidden="0" customHeight="1">
+    <x:row r="190" ht="48" hidden="0" customHeight="1">
       <x:c r="A190" s="19" t="str">
-        <x:v>sc_other</x:v>
+        <x:v>sc_seasonal</x:v>
       </x:c>
       <x:c r="B190" s="19" t="str">
         <x:v>收纳与家政</x:v>
       </x:c>
       <x:c r="C190" s="19" t="str">
+        <x:v>家政</x:v>
+      </x:c>
+      <x:c r="D190" s="19" t="str">
+        <x:v>换季物品存放</x:v>
+      </x:c>
+      <x:c r="E190" s="19" t="str">
+        <x:v>多选</x:v>
+      </x:c>
+      <x:c r="F190" s="22" t="str">
+        <x:v>被褥 / 羽绒服 / 电风扇 / 取暖器</x:v>
+      </x:c>
+      <x:c r="G190" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H190" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I190" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J190" s="22" t="str">
+        <x:v>顶柜预留</x:v>
+      </x:c>
+      <x:c r="K190" s="19" t="str">
+        <x:v>S3</x:v>
+      </x:c>
+      <x:c r="L190" s="22" t="str"/>
+    </x:row>
+    <x:row r="191" ht="36" hidden="0" customHeight="1">
+      <x:c r="A191" s="19" t="str">
+        <x:v>sc_other</x:v>
+      </x:c>
+      <x:c r="B191" s="19" t="str">
+        <x:v>收纳与家政</x:v>
+      </x:c>
+      <x:c r="C191" s="19" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="D190" s="19" t="str">
+      <x:c r="D191" s="19" t="str">
         <x:v>其他补充</x:v>
       </x:c>
-      <x:c r="E190" s="19" t="str">
+      <x:c r="E191" s="19" t="str">
         <x:v>长文本</x:v>
       </x:c>
-      <x:c r="F190" s="22" t="str">
+      <x:c r="F191" s="22" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G190" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H190" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I190" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J190" s="22" t="str">
+      <x:c r="G191" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H191" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I191" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J191" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K190" s="19" t="str">
+      <x:c r="K191" s="19" t="str">
         <x:v>本次重构</x:v>
       </x:c>
-      <x:c r="L190" s="22" t="str">
+      <x:c r="L191" s="22" t="str">
         <x:v>助手建议会写回这里</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="15" hidden="0" customHeight="1">
-      <x:c r="A191" s="27" t="str">
+    <x:row r="192" ht="15" hidden="0" customHeight="1">
+      <x:c r="A192" s="27" t="str">
         <x:v>note_free</x:v>
       </x:c>
-      <x:c r="B191" s="27" t="str">
+      <x:c r="B192" s="27" t="str">
         <x:v>补充说明</x:v>
       </x:c>
-      <x:c r="C191" s="27" t="str">
+      <x:c r="C192" s="27" t="str">
         <x:v>自由填写</x:v>
       </x:c>
-      <x:c r="D191" s="27" t="str">
+      <x:c r="D192" s="27" t="str">
         <x:v>其他补充需求</x:v>
       </x:c>
-      <x:c r="E191" s="27" t="str">
+      <x:c r="E192" s="27" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F191" s="28" t="str">
+      <x:c r="F192" s="28" t="str">
         <x:v>长文本</x:v>
       </x:c>
-      <x:c r="G191" s="29" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H191" s="29" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I191" s="29" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J191" s="28" t="str">
+      <x:c r="G192" s="29" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H192" s="29" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I192" s="29" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J192" s="28" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K191" s="27" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L191" s="28" t="str"/>
-    </x:row>
-    <x:row r="192" ht="24" hidden="0" customHeight="1">
-      <x:c r="A192" s="19" t="str">
+      <x:c r="K192" s="27" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L192" s="28" t="str"/>
+    </x:row>
+    <x:row r="193" ht="24" hidden="0" customHeight="1">
+      <x:c r="A193" s="19" t="str">
         <x:v>note_scene</x:v>
-      </x:c>
-      <x:c r="B192" s="19" t="str">
-        <x:v>补充说明</x:v>
-      </x:c>
-      <x:c r="C192" s="19" t="str">
-        <x:v>自由填写</x:v>
-      </x:c>
-      <x:c r="D192" s="19" t="str">
-        <x:v>畅想未来的生活场景</x:v>
-      </x:c>
-      <x:c r="E192" s="19" t="str">
-        <x:v>文本</x:v>
-      </x:c>
-      <x:c r="F192" s="22" t="str">
-        <x:v>长文本</x:v>
-      </x:c>
-      <x:c r="G192" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H192" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I192" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J192" s="22" t="str">
-        <x:v>场景化建议的输入</x:v>
-      </x:c>
-      <x:c r="K192" s="19" t="str">
-        <x:v>S5</x:v>
-      </x:c>
-      <x:c r="L192" s="22" t="str"/>
-    </x:row>
-    <x:row r="193" ht="15" hidden="0" customHeight="1">
-      <x:c r="A193" s="19" t="str">
-        <x:v>note_ref</x:v>
       </x:c>
       <x:c r="B193" s="19" t="str">
         <x:v>补充说明</x:v>
@@ -7306,94 +7308,130 @@
         <x:v>自由填写</x:v>
       </x:c>
       <x:c r="D193" s="19" t="str">
+        <x:v>畅想未来的生活场景</x:v>
+      </x:c>
+      <x:c r="E193" s="19" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="F193" s="22" t="str">
+        <x:v>长文本</x:v>
+      </x:c>
+      <x:c r="G193" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H193" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I193" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J193" s="22" t="str">
+        <x:v>场景化建议的输入</x:v>
+      </x:c>
+      <x:c r="K193" s="19" t="str">
+        <x:v>S5</x:v>
+      </x:c>
+      <x:c r="L193" s="22" t="str"/>
+    </x:row>
+    <x:row r="194" ht="15" hidden="0" customHeight="1">
+      <x:c r="A194" s="19" t="str">
+        <x:v>note_ref</x:v>
+      </x:c>
+      <x:c r="B194" s="19" t="str">
+        <x:v>补充说明</x:v>
+      </x:c>
+      <x:c r="C194" s="19" t="str">
+        <x:v>自由填写</x:v>
+      </x:c>
+      <x:c r="D194" s="19" t="str">
         <x:v>是否有参考图或效果图</x:v>
       </x:c>
-      <x:c r="E193" s="19" t="str">
-        <x:v>单选</x:v>
-      </x:c>
-      <x:c r="F193" s="22" t="str">
+      <x:c r="E194" s="19" t="str">
+        <x:v>单选</x:v>
+      </x:c>
+      <x:c r="F194" s="22" t="str">
         <x:v>有 / 无</x:v>
       </x:c>
-      <x:c r="G193" s="25" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H193" s="25" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I193" s="25" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J193" s="22" t="str">
+      <x:c r="G194" s="25" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H194" s="25" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I194" s="25" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J194" s="22" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K193" s="19" t="str">
-        <x:v>原件</x:v>
-      </x:c>
-      <x:c r="L193" s="22" t="str"/>
-    </x:row>
-    <x:row r="194" ht="15" hidden="0" customHeight="1">
-      <x:c r="A194" s="20" t="str">
+      <x:c r="K194" s="19" t="str">
+        <x:v>原件</x:v>
+      </x:c>
+      <x:c r="L194" s="22" t="str"/>
+    </x:row>
+    <x:row r="195" ht="15" hidden="0" customHeight="1">
+      <x:c r="A195" s="20" t="str">
         <x:v>note_process</x:v>
       </x:c>
-      <x:c r="B194" s="20" t="str">
+      <x:c r="B195" s="20" t="str">
         <x:v>补充说明</x:v>
       </x:c>
-      <x:c r="C194" s="20" t="str">
+      <x:c r="C195" s="20" t="str">
         <x:v>自由填写</x:v>
       </x:c>
-      <x:c r="D194" s="20" t="str">
+      <x:c r="D195" s="20" t="str">
         <x:v>对流程与沟通的要求</x:v>
       </x:c>
-      <x:c r="E194" s="20" t="str">
+      <x:c r="E195" s="20" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="F194" s="23" t="str">
+      <x:c r="F195" s="23" t="str">
         <x:v>文本</x:v>
       </x:c>
-      <x:c r="G194" s="26" t="str">
-        <x:v>选填</x:v>
-      </x:c>
-      <x:c r="H194" s="26" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-      <x:c r="I194" s="26" t="str">
-        <x:v>全部</x:v>
-      </x:c>
-      <x:c r="J194" s="23" t="str">
+      <x:c r="G195" s="26" t="str">
+        <x:v>选填</x:v>
+      </x:c>
+      <x:c r="H195" s="26" t="str">
+        <x:v>固定</x:v>
+      </x:c>
+      <x:c r="I195" s="26" t="str">
+        <x:v>全部</x:v>
+      </x:c>
+      <x:c r="J195" s="23" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K194" s="20" t="str">
+      <x:c r="K195" s="20" t="str">
         <x:v>S5</x:v>
       </x:c>
-      <x:c r="L194" s="23" t="str"/>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A196" s="30" t="str">
+      <x:c r="L195" s="23" t="str"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="30" t="str">
         <x:v>采集原则（量房前）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A197" s="31" t="str">
-        <x:v>1. 只问业主答得上来的：凭生活经验能回答、答错不会更糟、量房时由设计师问更合适的，移入「量房确认清单」。</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="31" t="str">
-        <x:v>2. 没有必填项：全部为「推荐填写」或「选填」，推荐填写不阻断提交，只影响完整度与侧栏提示。</x:v>
+        <x:v>1. 只问业主答得上来的：凭生活经验能回答、答错不会更糟、量房时由设计师问更合适的，移入「量房确认清单」。</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="31" t="str">
-        <x:v>3. 每个大类末尾都有「其他补充」，用户自由填写；助手采纳的建议也写回所属大类的「其他补充」并保留来源标记。</x:v>
+        <x:v>2. 没有必填项：全部为「推荐填写」或「选填」，推荐填写不阻断提交，只影响完整度与侧栏提示。</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="31" t="str">
-        <x:v>4. 可增删的空间实例：次卧（≤4）、卫生间（≤3，默认主卫与客卫）、书房/电竞房（≤2）；其余空间固定一个。</x:v>
+        <x:v>3. 每个大类末尾都有「其他补充」，用户自由填写；助手采纳的建议也写回所属大类的「其他补充」并保留来源标记。</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="31" t="str">
+        <x:v>4. 可增删的空间实例：次卧（≤4）、卫生间（≤3，默认主卫与客卫）、书房/电竞房（≤2）；其余空间固定一个。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="31" t="str">
         <x:v>5. 选项与填写并用：能被规则消费的用选项，无法枚举的用填写；不确定的地方提供「不清楚 / 听设计师建议」选项。</x:v>
       </x:c>
     </x:row>
